--- a/state/daysee_grants_latest.xlsx
+++ b/state/daysee_grants_latest.xlsx
@@ -63,7 +63,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -433,36 +433,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="48" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="43" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="48" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -563,28 +559,8 @@
           <t>detail_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>plan_background</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>plan_key_points</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>application_tips</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>raw_text</t>
-        </is>
-      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>115年度推動工作與生活平衡補助計畫</t>
@@ -592,22 +568,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 青年 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。 計畫重點 新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。 撰寫技巧 首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -649,19 +625,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -669,16 +653,8 @@
           <t>https://dayseechat.com/subsidy/grant-446/</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推動工作與生活平衡補助計畫 計畫來源 : 勞動部 補助對象 : 企業 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 青年 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。 計畫重點 新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。 撰寫技巧 首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>115年度數位服務創新補助計畫</t>
@@ -686,27 +662,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 100萬以上 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-18 創新創業 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。 計畫重點 高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。 撰寫技巧 首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -739,19 +715,27 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+          <t>https://moda.gov.tw/</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -759,16 +743,8 @@
           <t>https://dayseechat.com/subsidy/grant-448/</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度數位服務創新補助計畫 計畫來源 : 數位發展部 補助對象 : 企業 適用地區 : 不分縣市 補助金額 : 100萬以上 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-18 創新創業 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。 計畫重點 高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。 撰寫技巧 首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
     </row>
-    <row r="4">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
@@ -776,159 +752,135 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業 個人 民間團體</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>: 台中 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 產業發展 農漁村議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。 計畫重點 優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。 撰寫技巧 首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜農漁村議題</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-447/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>企業 民間團體</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展｜青年｜創新創業｜農漁村議題</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>婦女｜產業發展</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>婦女</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-447/</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年臺中市農業作物類生產設備設施改善補助計畫 計畫來源 : 縣市政府 補助對象 : 企業 個人 民間團體 適用地區 : 台中 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 產業發展 農漁村議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。 計畫重點 優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。 撰寫技巧 首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展｜青年</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
@@ -943,19 +895,27 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -963,16 +923,8 @@
           <t>https://dayseechat.com/subsidy/grant-438/</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推動工作與生活平衡補助計畫 計畫來源 : 勞動部 補助對象 : 企業 民間團體 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>115年度推展海內外客家事務交流合作活動補助</t>
@@ -980,22 +932,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>學校 民間團體</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 11萬-50萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 客家 文化藝文 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1005,24 +957,20 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>青年｜客家｜文化藝文</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>客家</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>文化藝文</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
@@ -1037,19 +985,27 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+          <t>https://www.hakka.gov.tw/chhakka/index</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/chhakka/index</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1057,16 +1013,8 @@
           <t>https://dayseechat.com/subsidy/grant-437/</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推展海內外客家事務交流合作活動補助 計畫來源 : 客家委員會 補助對象 : 學校 民間團體 適用地區 : 不分縣市 補助金額 : 11萬-50萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 客家 文化藝文 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>115年度原住民族促進就業獎勵計畫</t>
@@ -1074,32 +1022,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>原住民族委員會</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業 個人</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 原住民 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜青年｜原住民</t>
+          <t>產業發展｜原住民</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1109,14 +1057,10 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
           <t>原住民</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
@@ -1131,19 +1075,27 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1151,16 +1103,8 @@
           <t>https://dayseechat.com/subsidy/grant-439/</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度原住民族促進就業獎勵計畫 計畫來源 : 原住民族委員會 補助對象 : 企業 個人 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 原住民 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
@@ -1168,59 +1112,47 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>個人 其他對象 民間團體</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>: 台北 補助金額 : 51萬-100萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-06-30 生態環境 社區議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜青年｜創新創業｜文化藝文｜生態環境｜社區議題</t>
+          <t>生態環境｜社區議題</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
@@ -1261,16 +1193,8 @@
           <t>https://dayseechat.com/subsidy/grant-440/</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年臺北市住宅社區創能儲能及節能補助計畫 計畫來源 : 縣市政府 補助對象 : 個人 其他對象 民間團體 適用地區 : 台北 補助金額 : 51萬-100萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-06-30 生態環境 社區議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
     </row>
-    <row r="9">
+    <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>115年度補助原住民參加國家考試實施計畫</t>
@@ -1278,44 +1202,40 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>: 台中 補助金額 : 10萬以下 申請文件：點我前往主辦單位網站 截止日期 : 2026-11-30 原住民 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜原住民</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
           <t>原住民</t>
         </is>
       </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1331,32 +1251,32 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
+          <t>https://www.taichung.gov.tw/</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-441/</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度補助原住民參加國家考試實施計畫 計畫來源 : 縣市政府 補助對象 : 個人 適用地區 : 台中 補助金額 : 10萬以下 申請文件：點我前往主辦單位網站 截止日期 : 2026-11-30 原住民 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
         </is>
       </c>
     </row>
@@ -1374,33 +1294,33 @@
   <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="48" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="43" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="48" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="22" max="22"/>
+    <col width="42" customWidth="1" min="23" max="23"/>
+    <col width="56" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -1522,7 +1442,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>115年度推動工作與生活平衡補助計畫</t>
@@ -1530,22 +1450,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 青年 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。 計畫重點 新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。 撰寫技巧 首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1587,19 +1507,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -1607,16 +1535,108 @@
           <t>https://dayseechat.com/subsidy/grant-446/</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推動工作與生活平衡補助計畫 計畫來源 : 勞動部 補助對象 : 企業 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 青年 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。 計畫重點 新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。 撰寫技巧 首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年度推動工作與生活平衡補助計畫
+計畫來源 :
+勞動部
+補助對象 :
+企業
+適用地區 :
+不分縣市
+補助金額 :
+不分金額
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-05-31
+婦女
+產業發展
+青年
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+計畫背景
+企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。
+計畫重點
+新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。
+育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。
+身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。
+撰寫技巧
+首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度推動工作與生活平衡補助計畫
+＃關注議題：
+婦女
+產業發展
+＃補助對象：
+企業
+民間團體
+＃計畫來源：
+勞動部
+＃補助金額：
+不分金額
+72
+截止日期：2026-05-31
+衛生福利部社會及家庭署114年單親扶助計畫
+＃關注議題：
+婦女
+孩童
+身心障礙
+＃補助對象：
+個人
+＃計畫來源：
+衛生福利部
+＃補助金額：
+不分金額
+565
+截止日期：2026-10-06
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>115年度數位服務創新補助計畫</t>
@@ -1624,27 +1644,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 100萬以上 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-18 創新創業 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。 計畫重點 高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。 撰寫技巧 首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1677,19 +1697,27 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+          <t>https://moda.gov.tw/</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -1697,16 +1725,120 @@
           <t>https://dayseechat.com/subsidy/grant-448/</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度數位服務創新補助計畫 計畫來源 : 數位發展部 補助對象 : 企業 適用地區 : 不分縣市 補助金額 : 100萬以上 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-18 創新創業 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。 計畫重點 高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。 撰寫技巧 首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年度數位服務創新補助計畫
+計畫來源 :
+數位發展部
+補助對象 :
+企業
+適用地區 :
+不分縣市
+補助金額 :
+100萬以上
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-05-18
+創新創業
+產業發展
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+計畫背景
+數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。
+計畫重點
+高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。
+嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。
+聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。
+撰寫技巧
+首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度A+企業創新研發淬錬次世代通訊計畫
+＃關注議題：
+創新創業
+產業發展
+＃補助對象：
+企業
+民間團體
+＃計畫來源：
+經濟部
+＃補助金額：
+100萬以上
+33
+截止日期：2026-07-31
+115年度數位服務創新補助計畫
+＃關注議題：
+創新創業
+產業發展
+＃補助對象：
+企業
+＃計畫來源：
+數位發展部
+＃補助金額：
+不分金額
+147
+截止日期：2026-05-18
+115年度AI工具庫點數補助計畫
+＃關注議題：
+創新創業
+產業發展
+＃補助對象：
+企業
+＃計畫來源：
+經濟部
+＃補助金額：
+不分金額
+112
+截止日期：2026-10-30
+上一頁
+下一頁
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
@@ -1714,159 +1846,250 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業 個人 民間團體</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>: 台中 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 產業發展 農漁村議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。 計畫重點 優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。 撰寫技巧 首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜農漁村議題</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-447/</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年臺中市農業作物類生產設備設施改善補助計畫
+計畫來源 :
+縣市政府
+補助對象 :
+企業
+個人
+民間團體
+適用地區 :
+台中
+補助金額 :
+不分金額
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-04-30
+產業發展
+農漁村議題
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+計畫背景
+農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。
+計畫重點
+優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。
+排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。
+特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。
+撰寫技巧
+首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度推動工作與生活平衡補助計畫
+＃關注議題：
+婦女
+產業發展
+青年
+＃補助對象：
+企業
+＃計畫來源：
+勞動部
+＃補助金額：
+不分金額
+40
+截止日期：2026-05-31
+115年度數位服務創新補助計畫
+＃關注議題：
+創新創業
+產業發展
+＃補助對象：
+企業
+＃計畫來源：
+數位發展部
+＃補助金額：
+100萬以上
+51
+截止日期：2026-05-18
+115年度推動工作與生活平衡補助計畫
+＃關注議題：
+婦女
+產業發展
+＃補助對象：
+企業
+民間團體
+＃計畫來源：
+勞動部
+＃補助金額：
+不分金額
+72
+截止日期：2026-05-31
+上一頁
+下一頁
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>企業 民間團體</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展｜青年｜創新創業｜農漁村議題</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>婦女｜產業發展</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>婦女</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-447/</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年臺中市農業作物類生產設備設施改善補助計畫 計畫來源 : 縣市政府 補助對象 : 企業 個人 民間團體 適用地區 : 台中 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 產業發展 農漁村議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。 計畫重點 優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。 撰寫技巧 首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展｜青年</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
@@ -1881,19 +2104,27 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1901,16 +2132,110 @@
           <t>https://dayseechat.com/subsidy/grant-438/</t>
         </is>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推動工作與生活平衡補助計畫 計畫來源 : 勞動部 補助對象 : 企業 民間團體 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年度推動工作與生活平衡補助計畫
+計畫來源 :
+勞動部
+補助對象 :
+企業
+民間團體
+適用地區 :
+不分縣市
+補助金額 :
+不分金額
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-05-31
+婦女
+產業發展
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+【計畫背景】
+在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。
+勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。
+當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。
+【計畫重點】
+這是一項充滿溫度的政策資源，期待能帶來以下改變：
+補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。
+減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。
+深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。
+【撰寫技巧】
+為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法：
+首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。
+其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。
+最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度推動工作與生活平衡補助計畫
+＃關注議題：
+婦女
+產業發展
+青年
+＃補助對象：
+企業
+＃計畫來源：
+勞動部
+＃補助金額：
+不分金額
+40
+截止日期：2026-05-31
+衛生福利部社會及家庭署114年單親扶助計畫
+＃關注議題：
+婦女
+孩童
+身心障礙
+＃補助對象：
+個人
+＃計畫來源：
+衛生福利部
+＃補助金額：
+不分金額
+565
+截止日期：2026-10-06
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>115年度推展海內外客家事務交流合作活動補助</t>
@@ -1918,22 +2243,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>學校 民間團體</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 11萬-50萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 客家 文化藝文 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1943,24 +2268,20 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>青年｜客家｜文化藝文</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>客家</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>文化藝文</t>
         </is>
       </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
@@ -1975,19 +2296,27 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+          <t>https://www.hakka.gov.tw/chhakka/index</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/chhakka/index</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1995,16 +2324,111 @@
           <t>https://dayseechat.com/subsidy/grant-437/</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推展海內外客家事務交流合作活動補助 計畫來源 : 客家委員會 補助對象 : 學校 民間團體 適用地區 : 不分縣市 補助金額 : 11萬-50萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 客家 文化藝文 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年度推展海內外客家事務交流合作活動補助
+計畫來源 :
+客家委員會
+補助對象 :
+學校
+民間團體
+適用地區 :
+不分縣市
+補助金額 :
+11萬-50萬
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-04-30
+客家
+文化藝文
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+【計畫背景】
+文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。
+客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。
+我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。
+【計畫重點】
+這項補助著眼於深度的文化擾動，具體資源包含：
+最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。
+多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。
+跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。
+【撰寫技巧】
+在規劃這份充滿文化溫度的提案時，可以留意以下關鍵：
+第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。
+第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。
+第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度客家知識體系發展獎勵補助計畫
+＃關注議題：
+客家
+文化藝文
+＃補助對象：
+個人
+學校
+民間團體
+＃計畫來源：
+客家委員會
+＃補助金額：
+不分金額
+44
+截止日期：2026-04-30
+客家影像畢業製作孵育計畫徵選
+＃關注議題：
+客家
+文化藝文
+＃補助對象：
+學校
+＃計畫來源：
+客家委員會
+＃補助金額：
+11萬-50萬
+51萬-100萬
+136
+截止日期：2026-06-20
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>115年度原住民族促進就業獎勵計畫</t>
@@ -2012,32 +2436,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>原住民族委員會</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>企業 個人</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 原住民 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜青年｜原住民</t>
+          <t>產業發展｜原住民</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2047,14 +2471,10 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
           <t>原住民</t>
         </is>
       </c>
+      <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
@@ -2069,19 +2489,27 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -2089,16 +2517,95 @@
           <t>https://dayseechat.com/subsidy/grant-439/</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度原住民族促進就業獎勵計畫 計畫來源 : 原住民族委員會 補助對象 : 企業 個人 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 原住民 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年度原住民族促進就業獎勵計畫
+計畫來源 :
+原住民族委員會
+補助對象 :
+企業
+個人
+適用地區 :
+不分縣市
+補助金額 :
+不分金額
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-04-30
+原住民
+產業發展
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+【計畫背景】
+在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。
+原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。
+透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。
+【計畫重點】
+這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向：
+分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。
+鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。
+公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。
+【撰寫技巧】
+申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢：
+首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。
+其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。
+最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度補助原住民參加國家考試實施計畫
+＃關注議題：
+原住民
+＃補助對象：
+個人
+＃計畫來源：
+縣市政府
+＃補助金額：
+10萬以下
+24
+截止日期：2026-11-30
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
@@ -2106,59 +2613,47 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>個人 其他對象 民間團體</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>: 台北 補助金額 : 51萬-100萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-06-30 生態環境 社區議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜青年｜創新創業｜文化藝文｜生態環境｜社區議題</t>
+          <t>生態環境｜社區議題</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
@@ -2199,16 +2694,130 @@
           <t>https://dayseechat.com/subsidy/grant-440/</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年臺北市住宅社區創能儲能及節能補助計畫 計畫來源 : 縣市政府 補助對象 : 個人 其他對象 民間團體 適用地區 : 台北 補助金額 : 51萬-100萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-06-30 生態環境 社區議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年臺北市住宅社區創能儲能及節能補助計畫
+計畫來源 :
+縣市政府
+補助對象 :
+個人
+其他對象
+民間團體
+適用地區 :
+台北
+補助金額 :
+51萬-100萬
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-06-30
+生態環境
+社區議題
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+【計畫背景】
+走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。
+這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。
+透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。
+【計畫重點】
+要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持：
+最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。
+涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。
+凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。
+【撰寫技巧】
+要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法：
+第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。
+第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。
+第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度推動資源循環地方創生計畫
+＃關注議題：
+生態環境
+產業發展
+社區議題
+＃補助對象：
+企業
+民間團體
+＃計畫來源：
+環境部
+＃補助金額：
+100萬以上
+111
+截止日期：2026-07-06
+115年度基隆市機車產業輔導綠能轉型產業補助計畫
+＃關注議題：
+生態環境
+產業發展
+＃補助對象：
+企業
+＃計畫來源：
+縣市政府
+＃補助金額：
+10萬以下
+20
+截止日期：2026-12-15
+115年臺南青年公共參與行動計畫
+＃關注議題：
+創新創業
+文化藝文
+生態環境
+社區議題
+青年
+＃補助對象：
+個人
+學校
+民間團體
+＃計畫來源：
+縣市政府
+＃補助金額：
+10萬以下
+80
+截止日期：2026-04-30
+上一頁
+下一頁
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>115年度補助原住民參加國家考試實施計畫</t>
@@ -2216,44 +2825,40 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>: 台中 補助金額 : 10萬以下 申請文件：點我前往主辦單位網站 截止日期 : 2026-11-30 原住民 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜原住民</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
           <t>原住民</t>
         </is>
       </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
@@ -2269,19 +2874,27 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
+          <t>https://www.taichung.gov.tw/</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>bing_title_no_match</t>
+          <t>verified_portal_homepage</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -2289,12 +2902,100 @@
           <t>https://dayseechat.com/subsidy/grant-441/</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度補助原住民參加國家考試實施計畫 計畫來源 : 縣市政府 補助對象 : 個人 適用地區 : 台中 補助金額 : 10萬以下 申請文件：點我前往主辦單位網站 截止日期 : 2026-11-30 原住民 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
+          <t>首頁
+關於我們
+找資訊
+找知識
+找資源
+聯絡我們
+帳號設定
+註冊
+115年度補助原住民參加國家考試實施計畫
+計畫來源 :
+縣市政府
+補助對象 :
+個人
+適用地區 :
+台中
+補助金額 :
+10萬以下
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-11-30
+原住民
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+計畫背景
+為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。
+補助5大重點
+申請期限：即日起至115年11月30日止，若經費額滿將提前截止。
+適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。
+資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。
+補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。
+必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。
+計畫撰寫技巧
+確認發票規定
+務必確保發票為當年度開立，且日期必須在考試日期之前。
+到考證明清晰
+准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。
+補習班須合法
+報名前請先確認該補習機構為臺中市合法立案，以免不符資格。
+及早提出申請
+因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。
+文件準備齊全
+送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。
+返回主頁
+你可能也會喜歡這些資訊...
+115年度原住民族促進就業獎勵計畫
+＃關注議題：
+原住民
+產業發展
+＃補助對象：
+企業
+個人
+＃計畫來源：
+原住民族委員會
+＃補助金額：
+不分金額
+37
+截止日期：2026-04-30
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱</t>
         </is>
       </c>
     </row>
@@ -2309,14 +3010,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
@@ -2328,7 +3029,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>run_type</t>
@@ -2336,37 +3037,57 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>first_run</t>
+          <t>delta_run</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>new_count</t>
+          <t>current_count</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>previous_count</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>new_count</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>updated_count</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>0</v>
+      <c r="B6" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>removed_count</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2381,36 +3102,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="48" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="43" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="48" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -2509,802 +3226,6 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>detail_url</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>plan_background</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>plan_key_points</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>application_tips</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>raw_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 青年 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。 計畫重點 新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。 撰寫技巧 首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展｜青年</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-446/</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推動工作與生活平衡補助計畫 計畫來源 : 勞動部 補助對象 : 企業 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 青年 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。 計畫重點 新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。 撰寫技巧 首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>: 不分縣市 補助金額 : 100萬以上 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-18 創新創業 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。 計畫重點 高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。 撰寫技巧 首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜創新創業</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度數位服務創新補助計畫 計畫來源 : 數位發展部 補助對象 : 企業 適用地區 : 不分縣市 補助金額 : 100萬以上 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-18 創新創業 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。 計畫重點 高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。 撰寫技巧 首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>: 台中 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 產業發展 農漁村議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。 計畫重點 優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。 撰寫技巧 首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展｜青年｜創新創業｜農漁村議題</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-447/</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年臺中市農業作物類生產設備設施改善補助計畫 計畫來源 : 縣市政府 補助對象 : 企業 個人 民間團體 適用地區 : 台中 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 產業發展 農漁村議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。 計畫重點 優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。 撰寫技巧 首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展｜青年</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推動工作與生活平衡補助計畫 計畫來源 : 勞動部 補助對象 : 企業 民間團體 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-05-31 婦女 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>: 不分縣市 補助金額 : 11萬-50萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 客家 文化藝文 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>青年｜客家｜文化藝文</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度推展海內外客家事務交流合作活動補助 計畫來源 : 客家委員會 補助對象 : 學校 民間團體 適用地區 : 不分縣市 補助金額 : 11萬-50萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 客家 文化藝文 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>: 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 原住民 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜青年｜原住民</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度原住民族促進就業獎勵計畫 計畫來源 : 原住民族委員會 補助對象 : 企業 個人 適用地區 : 不分縣市 補助金額 : 不分金額 申請文件：點我前往主辦單位網站 截止日期 : 2026-04-30 原住民 產業發展 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>: 台北 補助金額 : 51萬-100萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-06-30 生態環境 社區議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜青年｜創新創業｜文化藝文｜生態環境｜社區議題</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-440/</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年臺北市住宅社區創能儲能及節能補助計畫 計畫來源 : 縣市政府 補助對象 : 個人 其他對象 民間團體 適用地區 : 台北 補助金額 : 51萬-100萬 申請文件：點我前往主辦單位網站 截止日期 : 2026-06-30 生態環境 社區議題 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 【計畫背景】 走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>: 台中 補助金額 : 10萬以下 申請文件：點我前往主辦單位網站 截止日期 : 2026-11-30 原住民 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜原住民</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-441/</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>首頁 關於我們 找資訊 找知識 找資源 聯絡我們 帳號設定 註冊 115年度補助原住民參加國家考試實施計畫 計畫來源 : 縣市政府 補助對象 : 個人 適用地區 : 台中 補助金額 : 10萬以下 申請文件：點我前往主辦單位網站 截止日期 : 2026-11-30 原住民 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主． ▎ 計畫簡介 計畫背景 為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。 必備文件：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。 計畫撰寫技巧 確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
         </is>
       </c>
     </row>
@@ -3319,37 +3240,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -3452,27 +3369,767 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>plan_background</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>plan_key_points</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>application_tips</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>raw_text</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
           <t>changed_fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>婦女｜產業發展｜青年</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-446/</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | organizer_site_url | official_organizer_site_url | official_url_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>數位發展部</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜創新創業</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-448/</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | organizer_site_url | official_organizer_site_url | official_url_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>企業 個人 民間團體</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜農漁村議題</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-447/</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>企業 民間團體</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>婦女｜產業發展</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-438/</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>客家委員會</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>學校 民間團體</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>客家｜文化藝文</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/chhakka/index</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/chhakka/index</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-437/</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>115年度原住民族促進就業獎勵計畫</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>原住民族委員會</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>企業 個人</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜原住民</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>115年度原住民族促進就業獎勵計畫</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-439/</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>個人 其他對象 民間團體</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51萬-100萬</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>生態環境｜社區議題</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-440/</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>個人</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>10萬以下</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-441/</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
         </is>
       </c>
     </row>
@@ -3487,36 +4144,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="29" customWidth="1" min="17" max="17"/>
-    <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
-    <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="18" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -3615,26 +4268,6 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>detail_url</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>plan_background</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>plan_key_points</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>application_tips</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>raw_text</t>
         </is>
       </c>
     </row>

--- a/state/daysee_grants_latest.xlsx
+++ b/state/daysee_grants_latest.xlsx
@@ -60,10 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -436,29 +439,29 @@
   <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="43" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -560,20 +563,20 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>原住民族委員會</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜個人</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -588,17 +591,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展｜青年</t>
+          <t>原住民｜產業發展</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -606,41 +609,37 @@
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -650,24 +649,24 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-446/</t>
+          <t>https://dayseechat.com/subsidy/grant-439/</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>數位發展部</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -677,27 +676,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜創新創業</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>客家</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -705,32 +704,32 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -740,11 +739,11 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
+          <t>https://dayseechat.com/subsidy/grant-437/</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
@@ -757,7 +756,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>企業 個人 民間團體</t>
+          <t>企業｜個人｜民間團體</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -834,20 +833,20 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -857,22 +856,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展</t>
+          <t>創新創業｜產業發展</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>創新創業</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -885,59 +884,59 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-448/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>客家委員會</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>學校 民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -947,27 +946,27 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>客家｜文化藝文</t>
+          <t>婦女｜產業發展</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>客家</t>
+          <t>婦女</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -975,32 +974,32 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1010,24 +1009,24 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
+          <t>https://dayseechat.com/subsidy/grant-438/</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>原住民族委員會</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>企業 個人</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1042,55 +1041,59 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜原住民</t>
+          <t>婦女｜產業發展｜青年</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1100,11 +1103,11 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
+          <t>https://dayseechat.com/subsidy/grant-446/</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
@@ -1117,7 +1120,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>個人 其他對象 民間團體</t>
+          <t>個人｜其他對象｜民間團體</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1194,7 +1197,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>115年度補助原住民參加國家考試實施計畫</t>
@@ -1251,27 +1254,19 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
@@ -1291,36 +1286,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
     <col width="42" customWidth="1" min="22" max="22"/>
     <col width="42" customWidth="1" min="23" max="23"/>
-    <col width="56" customWidth="1" min="24" max="24"/>
+    <col width="42" customWidth="1" min="24" max="24"/>
+    <col width="42" customWidth="1" min="25" max="25"/>
+    <col width="42" customWidth="1" min="26" max="26"/>
+    <col width="42" customWidth="1" min="27" max="27"/>
+    <col width="42" customWidth="1" min="28" max="28"/>
+    <col width="42" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -1328,491 +1328,361 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>detail_url</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>plan_source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>eligible_targets</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>applicable_region</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>grant_amount</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_site_url_raw</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_search_query</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_site_url</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>organizer_site_domain</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>official_organizer_site_url</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>official_organizer_domain</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>official_url_status</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>application_note</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>deadline_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>deadline_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>topic_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>topic_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>topic_3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>topic_4</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>topic_5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_url_raw</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_search_query</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_url</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>organizer_site_domain</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>official_organizer_site_url</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>official_organizer_domain</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>official_url_status</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>detail_url</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>plan_background</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>plan_key_points</t>
+          <t>background</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>application_tips</t>
+          <t>key_point_1</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>key_point_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>key_point_3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>key_point_4</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>key_point_5</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>writing_tips</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>raw_text</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>https://dayseechat.com/subsidy/grant-439/</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>原住民族委員會</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>企業｜個人</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>不分金額</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展｜青年</t>
+          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>https://www.cip.gov.tw/</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cip.gov.tw/</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>www.cip.gov.tw</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>原住民｜產業發展</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-446/</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。 育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。 身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>首頁
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" s="3" t="inlineStr"/>
+      <c r="X2" s="3" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
+      <c r="Z2" s="3" t="inlineStr"/>
+      <c r="AA2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>115年度原住民族促進就業獎勵計畫 - 小社區大事件
+首頁
 關於我們
+我們是誰
+發展歷程
+加入我們
 找資訊
 找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
 找資源
+數位導覽AI.Trip
+文創美編設計
 聯絡我們
 帳號設定
 註冊
-115年度推動工作與生活平衡補助計畫
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+115年度原住民族促進就業獎勵計畫
 計畫來源 :
-勞動部
+原住民族委員會
 補助對象 :
 企業
+個人
 適用地區 :
 不分縣市
 補助金額 :
 不分金額
 申請文件：點我前往主辦單位網站
 截止日期 :
-2026-05-31
-婦女
+2026-04-30
+原住民
 產業發展
-青年
 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
 ▎ 計畫簡介
+【
 計畫背景
-企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：勞動部公告），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。
+】
+在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。
+原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。
+透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。
+【
 計畫重點
-新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。
-育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。
-身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。
+】
+這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向：
+分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。
+鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。
+公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。
+【
 撰寫技巧
-首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。
+】
+申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢：
+首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。
+其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。
+最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。
 返回主頁
 你可能也會喜歡這些資訊...
-115年度推動工作與生活平衡補助計畫
+補助金額：10萬以下
+115年度補助原住民參加國家考試實施計畫
 ＃關注議題：
-婦女
-產業發展
-＃補助對象：
-企業
-民間團體
-＃計畫來源：
-勞動部
-＃補助金額：
-不分金額
-72
-截止日期：2026-05-31
-衛生福利部社會及家庭署114年單親扶助計畫
-＃關注議題：
-婦女
-孩童
-身心障礙
+原住民
 ＃補助對象：
 個人
 ＃計畫來源：
-衛生福利部
+縣市政府
 ＃補助金額：
-不分金額
-565
-截止日期：2026-10-06
-為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
-Copyright ©大事件行銷企劃有限公司
-快速選單
-首頁
-找資訊就是快-全國各式補助計畫
-找知識-文章
-找知識-影音
-找資源-社區發展數位工具
-找資本
-網站宣告
-隱私權政策
-服務條款
-聯絡小社區大事件
-聯絡我們
-236新北市土城區裕民路259巷5之1號9樓
-0901-128-536
-dayseechat@gmail.com
-FB粉絲頁
-訂閱電子報
-訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>數位發展部</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜創新創業</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://moda.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>moda.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>https://moda.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>moda.gov.tw</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。 嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。 聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。 返回主頁 你可能也會喜歡這些資訊... 115年度A+企業創新研發淬錬次世代通訊計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 經濟部 ＃補助金額： 100萬以上 33 截止日期：2026-07-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 不分金額 147 截止日期：2026-05-18 115年度AI工具庫點數補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 經濟部 ＃補助金額： 不分金額 112 截止日期：2026-10-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>首頁
-關於我們
-找資訊
-找知識
-找資源
-聯絡我們
-帳號設定
-註冊
-115年度數位服務創新補助計畫
-計畫來源 :
-數位發展部
-補助對象 :
-企業
-適用地區 :
-不分縣市
-補助金額 :
-100萬以上
-申請文件：點我前往主辦單位網站
-截止日期 :
-2026-05-18
-創新創業
-產業發展
-#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
-▎ 計畫簡介
-計畫背景
-數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：金融科技創新園區案例），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。
-計畫重點
-高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。
-嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。
-聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。
-撰寫技巧
-首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。
-返回主頁
-你可能也會喜歡這些資訊...
-115年度A+企業創新研發淬錬次世代通訊計畫
-＃關注議題：
-創新創業
-產業發展
-＃補助對象：
-企業
-民間團體
-＃計畫來源：
-經濟部
-＃補助金額：
-100萬以上
-33
-截止日期：2026-07-31
-115年度數位服務創新補助計畫
-＃關注議題：
-創新創業
-產業發展
-＃補助對象：
-企業
-＃計畫來源：
-數位發展部
-＃補助金額：
-不分金額
-147
-截止日期：2026-05-18
-115年度AI工具庫點數補助計畫
-＃關注議題：
-創新創業
-產業發展
-＃補助對象：
-企業
-＃計畫來源：
-經濟部
-＃補助金額：
-不分金額
-112
-截止日期：2026-10-30
+10萬以下
+24
+截止日期：2026-11-30
+無符合結果
 上一頁
 下一頁
 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
@@ -1824,7 +1694,16 @@
 找知識-影音
 找資源-社區發展數位工具
 找資本
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
 網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
 隱私權政策
 服務條款
 聯絡小社區大事件
@@ -1834,121 +1713,458 @@
 dayseechat@gmail.com
 FB粉絲頁
 訂閱電子報
-訂閱</t>
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>企業 個人 民間團體</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-437/</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>客家委員會</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>11萬-50萬</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hakka.gov.tw/</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>www.hakka.gov.tw</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜農漁村議題</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-447/</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。 特殊需求檢驗：若屬地區性特殊規格農機，必須具備農業試驗所檢測通過之證明文件。</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 115年度數位服務創新補助計畫 ＃關注議題： 創新創業 產業發展 ＃補助對象： 企業 ＃計畫來源： 數位發展部 ＃補助金額： 100萬以上 51 截止日期：2026-05-18 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 ＃補助對象： 企業 民間團體 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 72 截止日期：2026-05-31 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>首頁
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>客家｜文化藝文</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>115年度推展海內外客家事務交流合作活動補助 - 小社區大事件
+首頁
 關於我們
+我們是誰
+發展歷程
+加入我們
 找資訊
 找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
 找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+115年度推展海內外客家事務交流合作活動補助
+計畫來源 :
+客家委員會
+補助對象 :
+學校
+民間團體
+適用地區 :
+不分縣市
+補助金額 :
+11萬-50萬
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-04-30
+客家
+文化藝文
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+【
+計畫背景
+】
+文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。
+客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。
+我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。
+【
+計畫重點
+】
+這項補助著眼於深度的文化擾動，具體資源包含：
+最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。
+多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。
+跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。
+【
+撰寫技巧
+】
+在規劃這份充滿文化溫度的提案時，可以留意以下關鍵：
+第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。
+第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。
+第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。
+返回主頁
+你可能也會喜歡這些資訊...
+補助金額：不分金額
+115年度客家知識體系發展獎勵補助計畫
+＃關注議題：
+客家
+文化藝文
+＃補助對象：
+個人
+學校
+民間團體
+＃計畫來源：
+客家委員會
+＃補助金額：
+不分金額
+44
+截止日期：2026-04-30
+補助金額：11萬-50萬
+客家影像畢業製作孵育計畫徵選
+＃關注議題：
+客家
+文化藝文
+＃補助對象：
+學校
+＃計畫來源：
+客家委員會
+＃補助金額：
+11萬-50萬
+51萬-100萬
+136
+截止日期：2026-06-20
+無符合結果
+上一頁
+下一頁
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-447/</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>企業｜個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.taichung.gov.tw/</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>www.taichung.gov.tw</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展｜農漁村議題</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>115年臺中市農業作物類生產設備設施改善補助計畫 - 小社區大事件
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
 聯絡我們
 帳號設定
 註冊
@@ -1971,7 +2187,9 @@
 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
 ▎ 計畫簡介
 計畫背景
-農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：台中市政府農業局），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。
+農村勞動力老化與缺工問題已是不可逆的趨勢。此計畫的核心目標非常直接，就是透過設備補貼，協助產銷班與農民降低生產成本並提高良率。例如台中市許多果農已開始導入智慧農業或電動農機來減少人力依賴（來源：
+台中市政府農業局
+），官方期望藉由實質的硬體升級，維持地方農業競爭力，避免產能因缺工而崩盤。
 計畫重點
 優先補助項目：明訂智慧農業設備、碳匯農機與電動農機為三大優先核撥對象。
 排除低單價設備：售價新臺幣1萬元以下的農用機具直接排除，不予補助。
@@ -1980,6 +2198,7 @@
 首先，請直接瞄準「優先補助項目」進行採購規劃，申請傳統燃油機具的過件率將大幅降低。其次，申請書中的「效益評估」請直接填寫量化數據，例如導入某設備後可節省幾名人力、減少多少工時或提升多少產量，用具體的投資報酬率說服審查人員。最後，務必提前確認欲購買機型的售價與檢驗資格，以免因規格不符而白忙一場。
 返回主頁
 你可能也會喜歡這些資訊...
+補助金額：不分金額
 115年度推動工作與生活平衡補助計畫
 ＃關注議題：
 婦女
@@ -1993,6 +2212,7 @@
 不分金額
 40
 截止日期：2026-05-31
+補助金額：100萬以上
 115年度數位服務創新補助計畫
 ＃關注議題：
 創新創業
@@ -2005,6 +2225,7 @@
 100萬以上
 51
 截止日期：2026-05-18
+補助金額：不分金額
 115年度推動工作與生活平衡補助計畫
 ＃關注議題：
 婦女
@@ -2018,6 +2239,7 @@
 不分金額
 72
 截止日期：2026-05-31
+無符合結果
 上一頁
 下一頁
 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
@@ -2029,7 +2251,16 @@
 找知識-影音
 找資源-社區發展數位工具
 找資本
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
 網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
 隱私權政策
 服務條款
 聯絡小社區大事件
@@ -2039,117 +2270,458 @@
 dayseechat@gmail.com
 FB粉絲頁
 訂閱電子報
-訂閱</t>
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>https://dayseechat.com/subsidy/grant-448/</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展</t>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>創新創業｜產業發展</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。 【計畫重點】 這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>這是一項充滿溫度的政策資源，期待能帶來以下改變： 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。 【撰寫技巧】 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法： 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。 返回主頁 你可能也會喜歡這些資訊... 115年度推動工作與生活平衡補助計畫 ＃關注議題： 婦女 產業發展 青年 ＃補助對象： 企業 ＃計畫來源： 勞動部 ＃補助金額： 不分金額 40 截止日期：2026-05-31 衛生福利部社會及家庭署114年單親扶助計畫 ＃關注議題： 婦女 孩童 身心障礙 ＃補助對象： 個人 ＃計畫來源： 衛生福利部 ＃補助金額： 不分金額 565 截止日期：2026-10-06 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>首頁
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>115年度數位服務創新補助計畫 - 小社區大事件
+首頁
 關於我們
+我們是誰
+發展歷程
+加入我們
 找資訊
 找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
 找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+115年度數位服務創新補助計畫
+計畫來源 :
+數位發展部
+補助對象 :
+企業
+適用地區 :
+不分縣市
+補助金額 :
+100萬以上
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-05-18
+創新創業
+產業發展
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+計畫背景
+數位轉型已從口號轉為殘酷的市場淘汰賽。數位產業署推出此計畫，旨在補助軟體與資訊服務企業開發前瞻技術，不再只扮演代工角色，而是打造具備市場化價值的解決方案。過去如金融科技創新園區輔導的AI兒童感覺統合系統（來源：
+金融科技創新園區案例
+），即成功將數據演算商用化。官方期望藉此帶動各行業實質轉型。
+計畫重點
+高額度研發奧援：計畫總期程最高2年，每案補助經費上限高達新臺幣1500萬元。
+嚴格產業別限制：僅限登記為J582軟體出版業、J62電腦程式設計諮詢業、J63資訊服務業的企業申請。
+聚焦特定領域：規定從創新技術開發、企業營運應用、終端消費應用、社會公共應用及AI核心數位服務中擇一提案。
+撰寫技巧
+首先，財務結構是隱形門檻，申請前務必確認公司淨值為正數，否則初審將被淘汰。其次，提案簡報必須精準定義商業模式與關鍵績效指標，切勿將計畫書寫成純技術研發論文，審查委員重視的是系統如何落地變現。最後，經費編列請留意委託研究或行銷推廣費用的比例上限，將主力資源放在核心技術開發與人事費上。
+返回主頁
+你可能也會喜歡這些資訊...
+補助金額：100萬以上
+115年度A+企業創新研發淬錬次世代通訊計畫
+＃關注議題：
+創新創業
+產業發展
+＃補助對象：
+企業
+民間團體
+＃計畫來源：
+經濟部
+＃補助金額：
+100萬以上
+33
+截止日期：2026-07-31
+補助金額：不分金額
+115年度數位服務創新補助計畫
+＃關注議題：
+創新創業
+產業發展
+＃補助對象：
+企業
+＃計畫來源：
+數位發展部
+＃補助金額：
+不分金額
+147
+截止日期：2026-05-18
+補助金額：不分金額
+115年度AI工具庫點數補助計畫
+＃關注議題：
+創新創業
+產業發展
+＃補助對象：
+企業
+＃計畫來源：
+經濟部
+＃補助金額：
+不分金額
+112
+截止日期：2026-10-30
+無符合結果
+上一頁
+下一頁
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
+網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
+隱私權政策
+服務條款
+聯絡小社區大事件
+聯絡我們
+236新北市土城區裕民路259巷5之1號9樓
+0901-128-536
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-438/</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>企業｜民間團體</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>婦女｜產業發展</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫 - 小社區大事件
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
 聯絡我們
 帳號設定
 註冊
@@ -2170,22 +2742,29 @@
 產業發展
 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
 ▎ 計畫簡介
-【計畫背景】
+【
+計畫背景
+】
 在第一線陪伴在地企業的過程中，我們深刻體會到，員工的家庭安頓了，企業的發展才能真正穩健。
 勞動部的這項補助計畫是一座堅實的橋樑，協助雇主同理員工在工作與照顧之間的辛勞，進而打造充滿人情味的友善職場。
 當企業願意成為支持員工的土壤，這份公私協力的溫暖，將能有效凝聚內部共識，成為組織永續發展的最佳指南針。
-【計畫重點】
+【
+計畫重點
+】
 這是一項充滿溫度的政策資源，期待能帶來以下改變：
 補助多樣化的友善措施：從員工協助方案、中高齡身心健康講座，到辦理親子家庭日，皆有相對應的經費支持。
 減輕企業推動成本：透過政府實質的經費挹注，鼓勵中小企業踏出第一步，將對員工的關懷化為具體行動。
 深化職場培力與擾動：期待不只是舉辦單次活動，而是藉此擾動企業既有的制度，建立起長期的互助文化。
-【撰寫技巧】
+【
+撰寫技巧
+】
 為了讓這份善意順利獲得支持，在撰寫時請掌握幾個心法：
 首先、傾聽員工的真實需求：提案前不妨先做個小問卷，用數據與員工的真實回饋來說服委員，證明活動是真的切中需求。
 其次、規劃漸進式的陪伴策略：例如在推動員工協助方案時，說明如何以溫和保密的方式，陪伴面臨危機的夥伴度過難關。
 最後、展現高階主管的決心：在計畫書中具體承諾雇主將如何親身參與，這會讓委員看見你們推動友善職場的堅定意志。
 返回主頁
 你可能也會喜歡這些資訊...
+補助金額：不分金額
 115年度推動工作與生活平衡補助計畫
 ＃關注議題：
 婦女
@@ -2199,6 +2778,7 @@
 不分金額
 40
 截止日期：2026-05-31
+補助金額：不分金額
 衛生福利部社會及家庭署114年單親扶助計畫
 ＃關注議題：
 婦女
@@ -2212,9 +2792,18 @@
 不分金額
 565
 截止日期：2026-10-06
+無符合結果
+上一頁
+下一頁
 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
 Copyright ©大事件行銷企劃有限公司
 快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
 首頁
 找資訊就是快-全國各式補助計畫
 找知識-文章
@@ -2225,189 +2814,266 @@
 隱私權政策
 服務條款
 聯絡小社區大事件
+隱私權政策
+服務條款
+聯絡小社區大事件
 聯絡我們
 236新北市土城區裕民路259巷5之1號9樓
 0901-128-536
 dayseechat@gmail.com
 FB粉絲頁
 訂閱電子報
-訂閱</t>
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>客家委員會</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>學校 民間團體</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-446/</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>勞動部</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>客家｜文化藝文</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mol.gov.tw/</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>www.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>verified_portal_homepage</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。 客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。 我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。 【計畫重點】 這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>這項補助著眼於深度的文化擾動，具體資源包含： 最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。 多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。 跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。 【撰寫技巧】 在規劃這份充滿文化溫度的提案時，可以留意以下關鍵： 第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。 第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。 第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。 返回主頁 你可能也會喜歡這些資訊... 115年度客家知識體系發展獎勵補助計畫 ＃關注議題： 客家 文化藝文 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 客家委員會 ＃補助金額： 不分金額 44 截止日期：2026-04-30 客家影像畢業製作孵育計畫徵選 ＃關注議題： 客家 文化藝文 ＃補助對象： 學校 ＃計畫來源： 客家委員會 ＃補助金額： 11萬-50萬 51萬-100萬 136 截止日期：2026-06-20 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>首頁
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>婦女｜產業發展｜青年</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>115年度推動工作與生活平衡補助計畫 - 小社區大事件
+首頁
 關於我們
+我們是誰
+發展歷程
+加入我們
 找資訊
 找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
 找資源
+數位導覽AI.Trip
+文創美編設計
 聯絡我們
 帳號設定
 註冊
-115年度推展海內外客家事務交流合作活動補助
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+115年度推動工作與生活平衡補助計畫
 計畫來源 :
-客家委員會
+勞動部
 補助對象 :
-學校
-民間團體
+企業
 適用地區 :
 不分縣市
 補助金額 :
-11萬-50萬
+不分金額
 申請文件：點我前往主辦單位網站
 截止日期 :
-2026-04-30
-客家
-文化藝文
+2026-05-31
+婦女
+產業發展
+青年
 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
 ▎ 計畫簡介
-【計畫背景】
-文化傳承不該只是停留在書本上的文字，而是需要透過人群的互動，讓它在真實的土壤中生根發芽。
-客委會的這項交流補助，就像是一座連結在地與國際的橋樑，鼓勵學校與民間團體走出舒適圈，將客家文化的美好傳遞出去。
-我們期待透過這樣的公私協力，陪伴更多對客家事務有熱情的工作者，在海內外的交流中凝聚共識，讓世界聽見客庄的聲音。
-【計畫重點】
-這項補助著眼於深度的文化擾動，具體資源包含：
-最高 30 萬元的經費支持：針對國內外依法立案的民間團體及各級學校，提供辦理客家文化交流活動的實質後盾。
-多元化的活動形式：無論是具歷史傳承意義的區域性年會，或是促進多元文化對話的展演，都在支持之列。
-跨越國界的培力精神：期待藉由雙向的參訪與互動，不僅向外輸出台灣客家經驗，也為在地工作者帶回國際視野。
-【撰寫技巧】
-在規劃這份充滿文化溫度的提案時，可以留意以下關鍵：
-第一、找到獨特的文化切入點：不要只是舉辦走馬看花的觀光行程，請具體說明活動如何促成深度的跨文化對話。
-第二、描繪青年參與的軌跡：審查委員非常看重世代傳承，請在計畫中展現如何同理年輕人的語言焦慮，並溫和漸進地引導他們參與。
-第三、建立清晰的效益指標：用具體的參與人數、產出的影像紀錄或合作備忘錄，來佐證這場交流能為客庄帶來的長遠改變。
+計畫背景
+企業留才已成為經營的最大痛點，高壓環境導致的離職潮正反噬企業運作。勞動部此計畫的核心邏輯，是要求雇主將員工福祉視為經營成本的一部分。114年已有近七百家企業透過此計畫辦理員工紓壓與家庭日（來源：
+勞動部公告
+），官方提供實質經費，協助企業建立友善職場，藉此降低流動率並穩定產能。
+計畫重點
+新增單身聯誼：115年度首度將單身員工聯誼納入補助，並允許跨企業聯合辦理，擴大社交圈。
+育兒協助升級：針對企業設置員工子女臨時協助空間給予硬體補助，並將臨時陪伴人員時薪調高至300元。
+身心健康課程：持續補助企業辦理運動健身、情緒紓壓及親子活動等最受歡迎的友善家庭措施。
+撰寫技巧
+首先，放棄千篇一律的福委會制式活動，請從員工需求調查出發，在計畫書中列出數據證明該措施確實符合員工痛點。其次，若要申請托育協助與臨時陪伴人員補助，請務必先確認企業內部的硬體空間法規與消防安檢標準，避免核撥時產生爭議。最後，主動善用跨企業聯合辦理聯誼機制，能在資源整合上取得審查優勢。
 返回主頁
 你可能也會喜歡這些資訊...
-115年度客家知識體系發展獎勵補助計畫
+補助金額：不分金額
+115年度推動工作與生活平衡補助計畫
 ＃關注議題：
-客家
-文化藝文
+婦女
+產業發展
+＃補助對象：
+企業
+民間團體
+＃計畫來源：
+勞動部
+＃補助金額：
+不分金額
+72
+截止日期：2026-05-31
+補助金額：不分金額
+衛生福利部社會及家庭署114年單親扶助計畫
+＃關注議題：
+婦女
+孩童
+身心障礙
 ＃補助對象：
 個人
-學校
-民間團體
 ＃計畫來源：
-客家委員會
+衛生福利部
 ＃補助金額：
 不分金額
-44
-截止日期：2026-04-30
-客家影像畢業製作孵育計畫徵選
-＃關注議題：
-客家
-文化藝文
-＃補助對象：
-學校
-＃計畫來源：
-客家委員會
-＃補助金額：
-11萬-50萬
-51萬-100萬
-136
-截止日期：2026-06-20
+565
+截止日期：2026-10-06
+無符合結果
+上一頁
+下一頁
 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
 Copyright ©大事件行銷企劃有限公司
 快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
 首頁
 找資訊就是快-全國各式補助計畫
 找知識-文章
@@ -2418,180 +3084,6 @@
 隱私權政策
 服務條款
 聯絡小社區大事件
-聯絡我們
-236新北市土城區裕民路259巷5之1號9樓
-0901-128-536
-dayseechat@gmail.com
-FB粉絲頁
-訂閱電子報
-訂閱</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>原住民族委員會</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>企業 個人</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜原住民</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>www.cip.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>www.cip.gov.tw</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。 原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。 透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。 【計畫重點】 這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向： 分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。 鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。 公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。 【撰寫技巧】 申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢： 首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。 其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。 最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。 返回主頁 你可能也會喜歡這些資訊... 115年度補助原住民參加國家考試實施計畫 ＃關注議題： 原住民 ＃補助對象： 個人 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 24 截止日期：2026-11-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>首頁
-關於我們
-找資訊
-找知識
-找資源
-聯絡我們
-帳號設定
-註冊
-115年度原住民族促進就業獎勵計畫
-計畫來源 :
-原住民族委員會
-補助對象 :
-企業
-個人
-適用地區 :
-不分縣市
-補助金額 :
-不分金額
-申請文件：點我前往主辦單位網站
-截止日期 :
-2026-04-30
-原住民
-產業發展
-#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
-▎ 計畫簡介
-【計畫背景】
-在地方走踏的過程中，我們深知每一次的就業媒合，都是撐起一個原鄉家庭的重要橋樑。
-原民會推出的這項就業獎勵計畫，宛如溫暖的指南針，不僅鼓勵企業提供更多優質職缺，更陪伴原住民青年與失業勞工在職場上穩健前行。
-透過津貼的實質挹注，我們期盼能培力在地人才，讓他們在家鄉的土壤上安心扎根，綻放屬於自己的光芒。
-【計畫重點】
-這份補助計畫帶著溫和堅定的力量，重點包含以下幾個面向：
-分層級的實質陪伴：依據勞工的投保薪資，每月提供 3,000 元至 10,000 元不等的就業獎勵津貼。
-鼓勵長期穩定就業：連續在職加保滿 7 個月以上的夥伴，津貼額度將進一步提升，給予更安定的支持。
-公私協力的就業網絡：期待透過企業與政府的合作，擾動原民職場的活力，降低失業焦慮，建立更友善的工作環境。
-【撰寫技巧】
-申請津貼與計畫時，你可以透過這些方式讓行政流程更順暢：
-首先、細心盤點申請資格：請確認勞工是在 115 年 1 月 1 日起始受僱，並在同一單位加保滿 3 個月，確保符合規定。
-其次、善用數位工具輔助：陪伴長輩或不熟悉網路的勞工，透過原 JOB 人力資源網進行線上申請，展現團隊的同理擔憂與互助精神。
-最後、確實核對證明文件：溫和且謹慎地準備存摺影本與勞保明細，讓這份得來不易的資源能精準落實到需要的人手中。
-返回主頁
-你可能也會喜歡這些資訊...
-115年度補助原住民參加國家考試實施計畫
-＃關注議題：
-原住民
-＃補助對象：
-個人
-＃計畫來源：
-縣市政府
-＃補助金額：
-10萬以下
-24
-截止日期：2026-11-30
-為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
-Copyright ©大事件行銷企劃有限公司
-快速選單
-首頁
-找資訊就是快-全國各式補助計畫
-找知識-文章
-找知識-影音
-找資源-社區發展數位工具
-找資本
-網站宣告
 隱私權政策
 服務條款
 聯絡小社區大事件
@@ -2601,11 +3093,21 @@
 dayseechat@gmail.com
 FB粉絲頁
 訂閱電子報
-訂閱</t>
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
@@ -2613,105 +3115,159 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>https://dayseechat.com/subsidy/grant-440/</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>個人 其他對象 民間團體</t>
-        </is>
-      </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>個人｜其他對象｜民間團體</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>51萬-100萬</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.taipei/</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>www.gov.taipei</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>生態環境｜社區議題</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-440/</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。 【計畫重點】 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持： 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。 【撰寫技巧】 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法： 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。 返回主頁 你可能也會喜歡這些資訊... 115年度推動資源循環地方創生計畫 ＃關注議題： 生態環境 產業發展 社區議題 ＃補助對象： 企業 民間團體 ＃計畫來源： 環境部 ＃補助金額： 100萬以上 111 截止日期：2026-07-06 115年度基隆市機車產業輔導綠能轉型產業補助計畫 ＃關注議題： 生態環境 產業發展 ＃補助對象： 企業 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 20 截止日期：2026-12-15 115年臺南青年公共參與行動計畫 ＃關注議題： 創新創業 文化藝文 生態環境 社區議題 青年 ＃補助對象： 個人 學校 民間團體 ＃計畫來源： 縣市政府 ＃補助金額： 10萬以下 80 截止日期：2026-04-30 上一頁 下一頁 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>首頁
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr"/>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr"/>
+      <c r="AA8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫 - 小社區大事件
+首頁
 關於我們
+我們是誰
+發展歷程
+加入我們
 找資訊
 找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
 找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
 聯絡我們
 帳號設定
 註冊
@@ -2733,22 +3289,29 @@
 社區議題
 #本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
 ▎ 計畫簡介
-【計畫背景】
+【
+計畫背景
+】
 走入社區，我們時常聽見長輩對電費調漲的擔憂，這份擔憂其實是推動環境永續的最佳土壤。
 這項補助計畫就像是一盞探照燈，指引台北市的社區管委會與居民，將日常的耗能困境轉化為綠能轉型的契機。
 透過公私協力，我們不再只是被動節電，而是主動為社區種下創能與儲能的種子，讓環境與生活品質一同成長。
-【計畫重點】
+【
+計畫重點
+】
 要讓改變發生，需要資源的灌溉，這座橋樑能為你帶來以下實質支持：
 最高補助達 100 萬元：提供社區建置太陽能或風力等創能設施，並可搭配儲能系統，補貼額度達總經費的 49%。
 涵蓋多樣化節能方案：包含公共區域的能源管理系統、電梯電力回生裝置，以及玻璃隔熱膜等，從細節處減少耗損。
 凝聚共識的永續精神：期待透過設備升級，擾動社區居民對能源議題的關注，讓永續不再是口號，而是日常實踐。
-【撰寫技巧】
+【
+撰寫技巧
+】
 要寫出一份充滿溫度的提案，你可以嘗試以下幾個方法：
 第一、真誠呈現社區困境：用真實的電費數據搭配長輩的日常小故事，讓審查委員同理你們的辛勞。
 第二、強調居民培力過程：不要只寫硬體建置，請具體說明如何陪伴居民學習節能知識，展現計畫的社會影響力。
 第三、勾勒清晰的維護藍圖：補助是一時的，社區互助是長久的，請說明未來設備如何由社區志工共同維護，展現長遠的營運決心。
 返回主頁
 你可能也會喜歡這些資訊...
+補助金額：100萬以上
 115年度推動資源循環地方創生計畫
 ＃關注議題：
 生態環境
@@ -2763,6 +3326,7 @@
 100萬以上
 111
 截止日期：2026-07-06
+補助金額：10萬以下
 115年度基隆市機車產業輔導綠能轉型產業補助計畫
 ＃關注議題：
 生態環境
@@ -2775,6 +3339,7 @@
 10萬以下
 20
 截止日期：2026-12-15
+補助金額：10萬以下
 115年臺南青年公共參與行動計畫
 ＃關注議題：
 創新創業
@@ -2792,6 +3357,7 @@
 10萬以下
 80
 截止日期：2026-04-30
+無符合結果
 上一頁
 下一頁
 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
@@ -2803,7 +3369,16 @@
 找知識-影音
 找資源-社區發展數位工具
 找資本
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
 網站宣告
+隱私權政策
+服務條款
+聯絡小社區大事件
 隱私權政策
 服務條款
 聯絡小社區大事件
@@ -2813,11 +3388,21 @@
 dayseechat@gmail.com
 FB粉絲頁
 訂閱電子報
-訂閱</t>
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>115年度補助原住民參加國家考試實施計畫</t>
@@ -2825,105 +3410,147 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>https://dayseechat.com/subsidy/grant-441/</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>個人</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>台中</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>原住民</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
+          <t>bing_title_no_match</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>申請文件：點我前往主辦單位網站</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-441/</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>為鼓勵設籍臺中市之原住民積極參與國家考試，提升就業競爭力與公務體系服務參與率，臺中市政府原住民族事務委員會持續辦理國家考試補習費用補助計畫。透過實質的學費減免，減輕原住民考生的經濟負擔，協助其專心備考，進而順利取得專業證照或公職資格，促進原住民族群的社會階層流動與穩定就業。 補助5大重點 申請期限：即日起至115年11月30日止，若經費額滿將提前截止。 適用對象：具備原住民身分，且設籍臺中市連續滿4個月以上之民眾。 資格限制：須報名本市合法立案文教機構之課程，並確實參加115年度國家考試。 補助金額：每人最高補助補習學費新臺幣1萬元，未達1萬元則依實支實付。</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>：需檢附申請表、繳費發票正本、准考證到考證明及存摺影本等。</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>確認發票規定 務必確保發票為當年度開立，且日期必須在考試日期之前。 到考證明清晰 准考證影本必須蓋有考選部當日的到考證明印章，且字跡需清晰可辨。 補習班須合法 報名前請先確認該補習機構為臺中市合法立案，以免不符資格。 及早提出申請 因計畫經費有限，採「額滿即止」制，建議考完試後盡速送件。 文件準備齊全 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。 返回主頁 你可能也會喜歡這些資訊... 115年度原住民族促進就業獎勵計畫 ＃關注議題： 原住民 產業發展 ＃補助對象： 企業 個人 ＃計畫來源： 原住民族委員會 ＃補助金額： 不分金額 37 截止日期：2026-04-30 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。 Copyright ©大事件行銷企劃有限公司 快速選單 首頁 找資訊就是快-全國各式補助計畫 找知識-文章 找知識-影音 找資源-社區發展數位工具 找資本 網站宣告 隱私權政策 服務條款 聯絡小社區大事件 聯絡我們 236新北市土城區裕民路259巷5之1號9樓 0901-128-536 dayseechat@gmail.com FB粉絲頁 訂閱電子報 訂閱</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>首頁
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr"/>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr"/>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>115年度補助原住民參加國家考試實施計畫 - 小社區大事件
+首頁
 關於我們
+我們是誰
+發展歷程
+加入我們
 找資訊
 找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
 找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
 聯絡我們
 帳號設定
 註冊
@@ -2963,6 +3590,7 @@
 送件前仔細核對身分證、存摺封面、課程表等九項規定文件是否皆齊備。
 返回主頁
 你可能也會喜歡這些資訊...
+補助金額：不分金額
 115年度原住民族促進就業獎勵計畫
 ＃關注議題：
 原住民
@@ -2976,9 +3604,18 @@
 不分金額
 37
 截止日期：2026-04-30
+無符合結果
+上一頁
+下一頁
 為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
 Copyright ©大事件行銷企劃有限公司
 快速選單
+首頁
+找資訊就是快-全國各式補助計畫
+找知識-文章
+找知識-影音
+找資源-社區發展數位工具
+找資本
 首頁
 找資訊就是快-全國各式補助計畫
 找知識-文章
@@ -2989,13 +3626,26 @@
 隱私權政策
 服務條款
 聯絡小社區大事件
+隱私權政策
+服務條款
+聯絡小社區大事件
 聯絡我們
 236新北市土城區裕民路259巷5之1號9樓
 0901-128-536
 dayseechat@gmail.com
 FB粉絲頁
 訂閱電子報
-訂閱</t>
+訂閱
+為臺灣每個「小社區」發展，發出支持「大四箭」，歡迎到此平台找資訊、找知識、找資源、找資本。
+Copyright ©大事件行銷企劃有限公司
+聯絡我們
+234新北市永和區環河西路一段95巷19弄17號
+02 2924 5568
+dayseechat@gmail.com
+FB粉絲頁
+訂閱電子報
+訂閱
+×</t>
         </is>
       </c>
     </row>
@@ -3013,11 +3663,11 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
@@ -3029,66 +3679,66 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>run_type</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>delta_run</t>
-        </is>
+          <t>current_count</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>current_count</t>
+          <t>previous_count</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>previous_count</t>
+          <t>new_count</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>new_count</t>
+          <t>updated_count</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>removed_count</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>updated_count</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>removed_count</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:19:17</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3105,29 +3755,29 @@
   <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -3240,33 +3890,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="43" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>
@@ -3367,26 +4016,21 @@
           <t>detail_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>changed_fields</t>
-        </is>
-      </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>原住民族委員會</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜個人</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3401,17 +4045,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展｜青年</t>
+          <t>原住民｜產業發展</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -3419,41 +4063,37 @@
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度原住民族促進就業獎勵計畫</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>https://www.mol.gov.tw/</t>
+          <t>https://www.cip.gov.tw/</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>www.mol.gov.tw</t>
+          <t>www.cip.gov.tw</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -3463,29 +4103,24 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-446/</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | organizer_site_url | official_organizer_site_url | official_url_status</t>
+          <t>https://dayseechat.com/subsidy/grant-439/</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>數位發展部</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3495,27 +4130,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜創新創業</t>
+          <t>客家｜文化藝文</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>客家</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>創新創業</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -3523,32 +4158,32 @@
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
+          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>115年度數位服務創新補助計畫</t>
+          <t>115年度推展海內外客家事務交流合作活動補助</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>https://moda.gov.tw/</t>
+          <t>https://www.hakka.gov.tw/</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>moda.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -3558,16 +4193,11 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | organizer_site_url | official_organizer_site_url | official_url_status</t>
+          <t>https://dayseechat.com/subsidy/grant-437/</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
@@ -3580,7 +4210,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>企業 個人 民間團體</t>
+          <t>企業｜個人｜民間團體</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3656,26 +4286,21 @@
           <t>https://dayseechat.com/subsidy/grant-447/</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text</t>
-        </is>
-      </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>數位發展部</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>企業 民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3685,22 +4310,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>婦女｜產業發展</t>
+          <t>創新創業｜產業發展</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>婦女</t>
+          <t>創新創業</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3713,64 +4338,59 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
+          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>115年度數位服務創新補助計畫</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>https://moda.gov.tw/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>moda.gov.tw</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>verified_portal_homepage</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-448/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>客家委員會</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>學校 民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3780,27 +4400,27 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>客家｜文化藝文</t>
+          <t>婦女｜產業發展</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>客家</t>
+          <t>婦女</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>文化藝文</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -3808,32 +4428,32 @@
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
+          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakka.gov.tw/chhakka/index</t>
+          <t>https://www.mol.gov.tw/</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>www.hakka.gov.tw</t>
+          <t>www.mol.gov.tw</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -3843,59 +4463,54 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
+          <t>https://dayseechat.com/subsidy/grant-438/</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>原住民族委員會</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>企業 個人</t>
+          <t>個人｜其他對象｜民間團體</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>產業發展｜原住民</t>
+          <t>生態環境｜社區議題</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>原住民</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -3903,32 +4518,32 @@
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/zh-tw/index.html</t>
+          <t>https://www.gov.taipei/</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -3938,19 +4553,14 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
+          <t>https://dayseechat.com/subsidy/grant-440/</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3960,176 +4570,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>個人 其他對象 民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>生態環境｜社區議題</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
+          <t>原住民</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-440/</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
           <t>https://dayseechat.com/subsidy/grant-441/</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>plan_source | eligible_targets | applicable_region | grant_amount | deadline_date | deadline_text | organizer_site_url | official_organizer_site_url | official_url_status</t>
         </is>
       </c>
     </row>
@@ -4147,29 +4649,29 @@
   <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="34" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="24" customWidth="1" min="19" max="19"/>
-    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>title</t>

--- a/state/daysee_grants_latest.xlsx
+++ b/state/daysee_grants_latest.xlsx
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-04-25 20:19:17</t>
+          <t>2026-04-25 20:28:27</t>
         </is>
       </c>
     </row>
@@ -3890,10 +3890,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -3906,12 +3906,12 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="45" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
     <col width="27" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
     <col width="43" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -4020,37 +4020,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>原住民族委員會</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>企業｜個人</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>原住民｜產業發展</t>
+          <t>原住民</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -4058,578 +4058,38 @@
           <t>原住民</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
+          <t>115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cip.gov.tw/</t>
+          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>www.cip.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cip.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>www.cip.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>verified_portal_homepage</t>
+          <t>bing_title_no_match</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>客家委員會</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>客家｜文化藝文</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>企業｜個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展｜農漁村議題</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-447/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>數位發展部</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>創新創業｜產業發展</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>https://moda.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>moda.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>https://moda.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>moda.gov.tw</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>勞動部</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>婦女｜產業發展</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>個人｜其他對象｜民間團體</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>生態環境｜社區議題</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>verified_portal_homepage</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-440/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>bing_title_no_match</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-441/</t>
         </is>

--- a/state/daysee_grants_latest.xlsx
+++ b/state/daysee_grants_latest.xlsx
@@ -22494,7 +22494,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -22643,15 +22643,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -22659,9 +22659,9 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
-    <col width="31" customWidth="1" min="15" max="15"/>
-    <col width="48" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
@@ -22761,6085 +22761,6 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>official_url_confidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-446/</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>勞動部</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mol.gov.tw/</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>www.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-448/</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>數位發展部</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-447/</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>企業｜個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺中市農業作物類生產設備設施改善補助計畫</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-438/</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>勞動部</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-437/</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>客家委員會</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推展海內外客家事務交流合作活動補助</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-439/</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>原住民族委員會</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>企業｜個人</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度原住民族促進就業獎勵計畫</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-440/</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>個人｜其他對象｜民間團體</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-441/</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>原住民</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度補助原住民參加國家考試實施計畫</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>115年度A+企業創新研發淬錬次世代通訊計畫</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-442/</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度A%2B企業創新研發淬錬次世代通訊計畫</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>115年高照顧負荷家庭創新服務方案補助計畫</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-443/</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>基隆</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>身心障礙</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年高照顧負荷家庭創新服務方案補助計畫</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>115學年度精進童軍教育發展實施計畫</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-444/</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>教育部</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>學校</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115學年度精進童軍教育發展實施計畫</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>115年下半年度藝文及民俗節慶活動補助</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-445/</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年下半年度藝文及民俗節慶活動補助</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>高雄市政府會議展覽活動擴大補助計畫</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-435/</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>企業｜其他對象｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>高雄</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=高雄市政府會議展覽活動擴大補助計畫</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>115年度新竹縣社區營造計畫提案補助</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-436/</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>新竹</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下｜11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度新竹縣社區營造計畫提案補助</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-433/</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>基隆</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>身心障礙</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度基隆市政府補助辦理強化精神障礙者就業社區支持試辦計畫</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>115年度精神復健機構改善公共安全設施設備補助計畫</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-434/</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>衛生福利部</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>身心障礙</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度精神復健機構改善公共安全設施設備補助計畫</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-429/</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>數位發展部</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度數位服務創新補助計畫</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>115年度AI工具庫點數補助計畫</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-430/</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度AI工具庫點數補助計畫</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>115年促轉基金還原歷史真相旗艦計畫</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-431/</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>國家發展委員會</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>個人｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年促轉基金還原歷史真相旗艦計畫</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>115年智慧養殖創新事業補助計畫</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-432/</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>企業｜個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>雲林</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年智慧養殖創新事業補助計畫</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>115年教育優先區中小學暑假營隊活動補助</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-425/</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>教育部</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年教育優先區中小學暑假營隊活動補助</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
-      <c r="Q22" s="2" t="inlineStr"/>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>115年度彰化縣城鄉發展建設基金補助</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-426/</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>彰化</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度彰化縣城鄉發展建設基金補助</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>115年度中小微企業AI創新應用輔導計畫國際鏈結</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-427/</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度中小微企業AI創新應用輔導計畫國際鏈結</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
-      <c r="Q24" s="2" t="inlineStr"/>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-428/</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>新北</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年補助辦理兒童及少年未來教育與發展帳戶家戶訪視計畫</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>115年度彰化縣社區發展協會一般性補助</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-424/</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>彰化</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr"/>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>115年推動社區運動俱樂部實施計畫</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-418/</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>教育部</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>企業｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年推動社區運動俱樂部實施計畫</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-420/</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>新北</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr"/>
-      <c r="Q28" s="2" t="inlineStr"/>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>115年度彰化縣社區發展協會一般性補助</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-419/</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>彰化</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-10</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度彰化縣社區發展協會一般性補助</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>115年創新米糧產品量產暨市場拓銷計畫</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-421/</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>農業部</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年創新米糧產品量產暨市場拓銷計畫</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr"/>
-      <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>115年度紀錄片製作補助要點</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-423/</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>文化部</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度紀錄片製作補助要點</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動社區發展及互助共好補助計畫</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-408/</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>高齡</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動社區發展及互助共好補助計畫</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr"/>
-      <c r="Q32" s="2" t="inlineStr"/>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-410/</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>新北</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度新北市政府鼓勵廠商國內外參展補助計畫</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-409/</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>勞動部</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>企業｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr"/>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>115年度客家知識體系發展獎勵補助計畫</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-411/</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>客家委員會</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>個人｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度客家知識體系發展獎勵補助計畫</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動資源循環地方創生計畫</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-412/</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>環境部</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度推動資源循環地方創生計畫</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr"/>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>115年度新北市社區營造一般性計畫</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-414/</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>新北</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度新北市社區營造一般性計畫</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-415/</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>基隆</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度基隆市機車產業輔導綠能轉型產業補助計畫</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr"/>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>115年度商業服務業機器人應用輔導計畫</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-416/</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度商業服務業機器人應用輔導計畫</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>115年度台中拍獎勵電影事業計畫</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-417/</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度台中拍獎勵電影事業計畫</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr"/>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>115年度第2期臺北市電影製作補助</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-405/</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度第2期臺北市電影製作補助</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-407/</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr"/>
-      <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-406/</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>文化部</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr"/>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>115年臺南青年公共參與行動計畫</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-402/</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>個人｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>台南</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr"/>
-      <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>115年文化部青年村落文化行動計畫</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-394/</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>文化部</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr"/>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-395/</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr"/>
-      <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2026新竹市政府青年AI數位工具補助</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-399/</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>新竹</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P47" s="2" t="inlineStr"/>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>115年度不孕症試管嬰兒補助3.0方案</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-401/</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>衛生福利部</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上｜10萬以下｜11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr"/>
-      <c r="Q48" s="2" t="inlineStr"/>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>115年度台中市公寓大廈成立管理委員會補助</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-390/</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>其他對象｜民間團體</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-391/</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>台南</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr"/>
-      <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>115年臺南市民旅遊補助計畫</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-392/</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>台南</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>115年度第2期臺北市觀光活動補助</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-393/</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr"/>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>115年親海無礙海洋創生行動方案</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-375/</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>海洋委員會</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115年親海無礙海洋創生行動方案</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>2026-2027高雄馬祖團體旅遊補助計畫</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-383/</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>連江｜高雄</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>2027-03-31</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr"/>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-385/</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>台南</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.twtainan.net/</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>www.twtainan.net</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-381/</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>其他對象</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>高雄</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-01</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-380/</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>台南</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上｜10萬以下</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr"/>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>115年度新北市低碳社區改造補助</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-378/</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>其他對象</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>新北</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下｜11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>www.epd.ntpc.gov.tw</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>www.epd.ntpc.gov.tw</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-387/</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>文化部</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下｜11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>www.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>www.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>115年度台中市都市更新整建維護補助計畫</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-369/</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/3234351/post</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.taichung.gov.tw/3234351/post</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>www.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-370/</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>thd.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>thd.taichung.gov.tw</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-371/</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-363/</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>台北</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.industry-incentive.taipei/</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>www.industry-incentive.taipei</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr"/>
-      <c r="Q63" s="2" t="inlineStr"/>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>115年度小型企業創新研發計畫SBIR</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-365/</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>https://sbir.org.tw/</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>sbir.org.tw</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr"/>
-      <c r="Q64" s="2" t="inlineStr"/>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-368/</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>勞動部</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>企業｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>高齡</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>wlb.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>wlb.mol.gov.tw</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-361/</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>彰化</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>www.chcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>www.chcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>商業服務業AI解決方案補助計畫</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-359/</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>www.smebiz.org.tw</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr"/>
-      <c r="Q67" s="2" t="inlineStr"/>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-351/</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>桃園</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>tyoem.tycg.gov.tw</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>tyoem.tycg.gov.tw</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>中小企業接班轉型計畫</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-353/</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>www.value-chain.com.tw</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr"/>
-      <c r="Q69" s="2" t="inlineStr"/>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-356/</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>keid.nat.gov.tw</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>keid.nat.gov.tw</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>雙百萬運動漫畫徵選</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-344/</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>文化部</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>企業｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S71" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>115年桃園市智慧科技農業專案補助計畫</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-345/</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>桃園</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>農漁村議題</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>www.guishan.tycg.gov.tw</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>www.guishan.tycg.gov.tw</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S72" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>商業服務業AI解決方案補助計畫</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-349/</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>2027-10-20</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>www.smebiz.org.tw</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr"/>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S73" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>基隆市青年參與公益活動補助計畫</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-389/</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>基隆</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
-      <c r="N74" s="2" t="inlineStr">
-        <is>
-          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>dsa.dyhu.edu.tw</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="inlineStr"/>
-      <c r="Q74" s="2" t="inlineStr"/>
-      <c r="R74" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S74" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>115年度推動事業單位辦理職前培訓計畫</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-334/</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>勞動部</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>企業｜學校</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>台中</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="inlineStr">
-        <is>
-          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
-        </is>
-      </c>
-      <c r="O75" s="2" t="inlineStr">
-        <is>
-          <t>tcnr.wda.gov.tw</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="inlineStr">
-        <is>
-          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
-        </is>
-      </c>
-      <c r="Q75" s="2" t="inlineStr">
-        <is>
-          <t>tcnr.wda.gov.tw</t>
-        </is>
-      </c>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S75" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>親愛文化攜手計畫</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-336/</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>南投</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="inlineStr">
-        <is>
-          <t>https://cacf.easy.co/pages/support</t>
-        </is>
-      </c>
-      <c r="O76" s="2" t="inlineStr">
-        <is>
-          <t>cacf.easy.co</t>
-        </is>
-      </c>
-      <c r="P76" s="2" t="inlineStr"/>
-      <c r="Q76" s="2" t="inlineStr"/>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S76" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-331/</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>基隆</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上｜10萬以下</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>高齡</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>www.klcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
-        </is>
-      </c>
-      <c r="Q77" s="2" t="inlineStr">
-        <is>
-          <t>www.klcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="R77" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S77" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>115年度高雄市觀光行銷推廣補助計畫</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-327/</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>高雄</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下｜11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>https://khh.travel/zh-tw/event/news/7268/</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>khh.travel</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr"/>
-      <c r="Q78" s="2" t="inlineStr"/>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>115年度補助文化活動作業</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-314/</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>基隆</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>klctb.klcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
-        </is>
-      </c>
-      <c r="Q79" s="2" t="inlineStr">
-        <is>
-          <t>klctb.klcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="R79" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S79" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>115年海洋保育國際交流活動獎助計畫</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-319/</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>海洋委員會</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>個人｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下｜11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
-      <c r="N80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>www.oca.gov.tw</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
-        </is>
-      </c>
-      <c r="Q80" s="2" t="inlineStr">
-        <is>
-          <t>www.oca.gov.tw</t>
-        </is>
-      </c>
-      <c r="R80" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S80" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>全國性運動團體辦理全民運動相關活動計畫</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-300/</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>2026-12-15</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>isports.sa.gov.tw</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
-        </is>
-      </c>
-      <c r="Q81" s="2" t="inlineStr">
-        <is>
-          <t>isports.sa.gov.tw</t>
-        </is>
-      </c>
-      <c r="R81" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S81" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>客家影像畢業製作孵育計畫徵選</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-294/</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>客家委員會</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>學校</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
-        </is>
-      </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="P82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="R82" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>115年品牌臺東產業行銷補助</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-284/</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>台東</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>10萬以下｜11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>bdsone.taitung.gov.tw</t>
-        </is>
-      </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
-        <is>
-          <t>bdsone.taitung.gov.tw</t>
-        </is>
-      </c>
-      <c r="R83" s="2" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S83" s="2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-246/</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>衛生福利部</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>身心障礙</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P84" s="2" t="inlineStr"/>
-      <c r="Q84" s="2" t="inlineStr"/>
-      <c r="R84" s="2" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S84" s="2" t="inlineStr">
-        <is>
-          <t>low</t>
         </is>
       </c>
     </row>

--- a/state/daysee_grants_latest.xlsx
+++ b/state/daysee_grants_latest.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3425,17 +3425,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-407/</t>
+          <t>https://dayseechat.com/subsidy/grant-406/</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3455,13 +3455,13 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -3470,7 +3470,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3494,52 +3494,68 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
+          <t>115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-406/</t>
+          <t>https://dayseechat.com/subsidy/grant-402/</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>個人｜學校｜民間團體</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>青年</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
+          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3563,68 +3579,52 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>115年臺南青年公共參與行動計畫</t>
+          <t>115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-402/</t>
+          <t>https://dayseechat.com/subsidy/grant-394/</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>個人｜學校｜民間團體</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
+          <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3648,22 +3648,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>115年文化部青年村落文化行動計畫</t>
+          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-394/</t>
+          <t>https://dayseechat.com/subsidy/grant-395/</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>經濟部</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3673,27 +3673,31 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>創新創業</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
+          <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3717,56 +3721,52 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+          <t>2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-395/</t>
+          <t>https://dayseechat.com/subsidy/grant-399/</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>新竹</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>創新創業</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
+          <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3790,17 +3790,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026新竹市政府青年AI數位工具補助</t>
+          <t>115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-399/</t>
+          <t>https://dayseechat.com/subsidy/grant-401/</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>新竹</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>100萬以上｜10萬以下｜11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3826,7 +3826,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>青年</t>
+          <t>孩童</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -3835,7 +3835,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
+          <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3859,43 +3859,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>115年度不孕症試管嬰兒補助3.0方案</t>
+          <t>115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-401/</t>
+          <t>https://dayseechat.com/subsidy/grant-390/</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>其他對象｜民間團體</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>100萬以上｜10萬以下｜11萬-50萬｜51萬-100萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>孩童</t>
+          <t>社區議題</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
+          <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3928,12 +3928,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>115年度台中市公寓大廈成立管理委員會補助</t>
+          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-390/</t>
+          <t>https://dayseechat.com/subsidy/grant-391/</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>其他對象｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3958,22 +3958,26 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
+          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3997,12 +4001,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-391/</t>
+          <t>https://dayseechat.com/subsidy/grant-392/</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4027,26 +4031,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
           <t>產業發展</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4070,12 +4070,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>115年臺南市民旅遊補助計畫</t>
+          <t>115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-392/</t>
+          <t>https://dayseechat.com/subsidy/grant-393/</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4085,22 +4085,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
+          <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4139,27 +4139,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>115年度第2期臺北市觀光活動補助</t>
+          <t>115年親海無礙海洋創生行動方案</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-393/</t>
+          <t>https://dayseechat.com/subsidy/grant-375/</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>海洋委員會</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4169,22 +4169,26 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
+          <t>https://www.google.com/search?q=115年親海無礙海洋創生行動方案</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4208,56 +4212,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>115年親海無礙海洋創生行動方案</t>
+          <t>2026-2027高雄馬祖團體旅遊補助計畫</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-375/</t>
+          <t>https://dayseechat.com/subsidy/grant-383/</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>學校｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>連江｜高雄</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年親海無礙海洋創生行動方案</t>
+          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4281,12 +4281,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-2027高雄馬祖團體旅遊補助計畫</t>
+          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-383/</t>
+          <t>https://dayseechat.com/subsidy/grant-385/</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>連江｜高雄</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2027-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -4326,36 +4326,36 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
+          <t>https://www.twtainan.net/</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>www.google.com</t>
+          <t>www.twtainan.net</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>search_no_match</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
+          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-385/</t>
+          <t>https://dayseechat.com/subsidy/grant-381/</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4365,28 +4365,28 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>其他對象</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>高雄</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
@@ -4395,36 +4395,36 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://www.twtainan.net/</t>
+          <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>www.twtainan.net</t>
+          <t>www.google.com</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>search_no_match</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
+          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-381/</t>
+          <t>https://dayseechat.com/subsidy/grant-380/</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4434,28 +4434,28 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>其他對象</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>高雄</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>不分金額</t>
+          <t>100萬以上｜10萬以下</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -4464,7 +4464,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
+          <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4488,12 +4488,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
+          <t>115年度新北市低碳社區改造補助</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-380/</t>
+          <t>https://dayseechat.com/subsidy/grant-378/</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4503,125 +4503,133 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>其他對象</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>新北</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>100萬以上｜10萬以下</t>
+          <t>10萬以下｜11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>社區議題</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+          <t>www.epd.ntpc.gov.tw</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>www.epd.ntpc.gov.tw</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>search_no_match</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>115年度新北市低碳社區改造補助</t>
+          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-378/</t>
+          <t>https://dayseechat.com/subsidy/grant-387/</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>其他對象</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>新北</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬｜51萬-100萬</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
           <t>社區議題</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>www.epd.ntpc.gov.tw</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
+          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>www.epd.ntpc.gov.tw</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4638,37 +4646,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
+          <t>115年度台中市都市更新整建維護補助計畫</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-387/</t>
+          <t>https://dayseechat.com/subsidy/grant-369/</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>個人</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>10萬以下｜11萬-50萬</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -4683,22 +4691,22 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
+          <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>www.moc.gov.tw</t>
+          <t>www.taichung.gov.tw</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -4715,12 +4723,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>115年度台中市都市更新整建維護補助計畫</t>
+          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-369/</t>
+          <t>https://dayseechat.com/subsidy/grant-370/</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4740,12 +4748,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -4760,22 +4768,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/3234351/post</t>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
+          <t>thd.taichung.gov.tw</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.taichung.gov.tw/3234351/post</t>
+          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>www.taichung.gov.tw</t>
+          <t>thd.taichung.gov.tw</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -4792,12 +4800,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
+          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-370/</t>
+          <t>https://dayseechat.com/subsidy/grant-371/</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4807,52 +4815,56 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>台北</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>thd.taichung.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
+          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>thd.taichung.gov.tw</t>
+          <t>www.gov.taipei</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -4869,12 +4881,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
+          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-371/</t>
+          <t>https://dayseechat.com/subsidy/grant-363/</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4884,7 +4896,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4894,73 +4906,61 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>社區議題</t>
-        </is>
-      </c>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
+          <t>https://www.industry-incentive.taipei/</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>www.gov.taipei</t>
-        </is>
-      </c>
+          <t>www.industry-incentive.taipei</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
+          <t>115年度小型企業創新研發計畫SBIR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-363/</t>
+          <t>https://dayseechat.com/subsidy/grant-365/</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>經濟部</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>台北</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4995,12 +4995,12 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://www.industry-incentive.taipei/</t>
+          <t>https://sbir.org.tw/</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>www.industry-incentive.taipei</t>
+          <t>sbir.org.tw</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -5019,22 +5019,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>115年度小型企業創新研發計畫SBIR</t>
+          <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-365/</t>
+          <t>https://dayseechat.com/subsidy/grant-368/</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜學校｜民間團體</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5044,18 +5044,18 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>高齡</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
@@ -5064,67 +5064,75 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://sbir.org.tw/</t>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>sbir.org.tw</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
+          <t>wlb.mol.gov.tw</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>wlb.mol.gov.tw</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>115年度推動工作與生活平衡補助計畫</t>
+          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-368/</t>
+          <t>https://dayseechat.com/subsidy/grant-361/</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>企業｜學校｜民間團體</t>
+          <t>企業</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>彰化</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>高齡</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -5133,22 +5141,22 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>wlb.mol.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
+          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>wlb.mol.gov.tw</t>
+          <t>www.chcg.gov.tw</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -5165,17 +5173,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
+          <t>商業服務業AI解決方案補助計畫</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-361/</t>
+          <t>https://dayseechat.com/subsidy/grant-359/</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>經濟部</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5185,7 +5193,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>彰化</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5195,7 +5203,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -5210,49 +5218,41 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>www.chcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>www.chcg.gov.tw</t>
-        </is>
-      </c>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>商業服務業AI解決方案補助計畫</t>
+          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-359/</t>
+          <t>https://dayseechat.com/subsidy/grant-351/</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5262,23 +5262,23 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>桃園</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -5287,91 +5287,103 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>www.smebiz.org.tw</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
+          <t>tyoem.tycg.gov.tw</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>tyoem.tycg.gov.tw</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
+          <t>雙百萬運動漫畫徵選</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-351/</t>
+          <t>https://dayseechat.com/subsidy/grant-344/</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>企業｜學校｜民間團體</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>桃園</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>tyoem.tycg.gov.tw</t>
+          <t>grants.moc.gov.tw</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>tyoem.tycg.gov.tw</t>
+          <t>grants.moc.gov.tw</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -5388,37 +5400,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>中小企業接班轉型計畫</t>
+          <t>115年桃園市智慧科技農業專案補助計畫</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-353/</t>
+          <t>https://dayseechat.com/subsidy/grant-345/</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>桃園</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -5427,42 +5439,54 @@
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>農漁村議題</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>www.value-chain.com.tw</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+          <t>www.guishan.tycg.gov.tw</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>www.guishan.tycg.gov.tw</t>
+        </is>
+      </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助</t>
+          <t>商業服務業AI解決方案補助計畫</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-356/</t>
+          <t>https://dayseechat.com/subsidy/grant-349/</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5482,12 +5506,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2027-10-20</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -5502,150 +5526,130 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>keid.nat.gov.tw</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>keid.nat.gov.tw</t>
-        </is>
-      </c>
+          <t>www.smebiz.org.tw</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>雙百萬運動漫畫徵選</t>
+          <t>基隆市青年參與公益活動補助計畫</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-344/</t>
+          <t>https://dayseechat.com/subsidy/grant-389/</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>文化部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>企業｜學校｜民間團體</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>基隆</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
+          <t>青年</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
+          <t>dsa.dyhu.edu.tw</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>115年桃園市智慧科技農業專案補助計畫</t>
+          <t>115年度推動事業單位辦理職前培訓計畫</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-345/</t>
+          <t>https://dayseechat.com/subsidy/grant-334/</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>勞動部</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>企業｜學校</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>桃園</t>
+          <t>台中</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>11萬-50萬｜51萬-100萬</t>
+          <t>51萬-100萬</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -5656,7 +5660,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>農漁村議題</t>
+          <t>青年</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -5664,22 +5668,22 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>www.guishan.tycg.gov.tw</t>
+          <t>tcnr.wda.gov.tw</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
+          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>www.guishan.tycg.gov.tw</t>
+          <t>tcnr.wda.gov.tw</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -5696,43 +5700,43 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>商業服務業AI解決方案補助計畫</t>
+          <t>親愛文化攜手計畫</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-349/</t>
+          <t>https://dayseechat.com/subsidy/grant-336/</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>企業</t>
+          <t>學校｜民間團體</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>南投</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>11萬-50萬</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2027-10-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -5741,12 +5745,12 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
+          <t>https://cacf.easy.co/pages/support</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>www.smebiz.org.tw</t>
+          <t>cacf.easy.co</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -5765,12 +5769,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>基隆市青年參與公益活動補助計畫</t>
+          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-389/</t>
+          <t>https://dayseechat.com/subsidy/grant-331/</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5780,7 +5784,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>學校｜民間團體</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5790,81 +5794,93 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>100萬以上｜10萬以下</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>青年</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr"/>
+          <t>社區議題</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>高齡</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>dsa.dyhu.edu.tw</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>www.klcg.gov.tw</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>115年度推動事業單位辦理職前培訓計畫</t>
+          <t>115年度高雄市觀光行銷推廣補助計畫</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-334/</t>
+          <t>https://dayseechat.com/subsidy/grant-327/</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>勞動部</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>企業｜學校</t>
+          <t>民間團體</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>台中</t>
+          <t>高雄</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>51萬-100萬</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -5873,54 +5889,42 @@
           <t>產業發展</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>青年</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>tcnr.wda.gov.tw</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>tcnr.wda.gov.tw</t>
-        </is>
-      </c>
+          <t>khh.travel</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>親愛文化攜手計畫</t>
+          <t>115年度補助文化活動作業</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-336/</t>
+          <t>https://dayseechat.com/subsidy/grant-314/</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5930,22 +5934,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>學校｜民間團體</t>
+          <t>個人｜民間團體</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>南投</t>
+          <t>基隆</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>11萬-50萬</t>
+          <t>10萬以下</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -5960,56 +5964,64 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://cacf.easy.co/pages/support</t>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>cacf.easy.co</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+          <t>klctb.klcg.gov.tw</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>klctb.klcg.gov.tw</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>direct_non_google</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
+          <t>115年海洋保育國際交流活動獎助計畫</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-331/</t>
+          <t>https://dayseechat.com/subsidy/grant-319/</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>海洋委員會</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>個人｜學校｜民間團體</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>100萬以上｜10萬以下</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6020,35 +6032,31 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>社區議題</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>高齡</t>
-        </is>
-      </c>
+          <t>生態環境</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>www.klcg.gov.tw</t>
+          <t>www.oca.gov.tw</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
+          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>www.klcg.gov.tw</t>
+          <t>www.oca.gov.tw</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -6065,12 +6073,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>115年度高雄市觀光行銷推廣補助計畫</t>
+          <t>全國性運動團體辦理全民運動相關活動計畫</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-327/</t>
+          <t>https://dayseechat.com/subsidy/grant-300/</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6083,21 +6091,25 @@
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>100萬以上</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>生態環境</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -6106,91 +6118,103 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-327/</t>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>dayseechat.com</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
+          <t>isports.sa.gov.tw</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>isports.sa.gov.tw</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>search_no_match</t>
+          <t>direct_official</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>115年度補助文化活動作業</t>
+          <t>客家影像畢業製作孵育計畫徵選</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-314/</t>
+          <t>https://dayseechat.com/subsidy/grant-294/</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>客家委員會</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>個人｜民間團體</t>
+          <t>學校</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>基隆</t>
+          <t>不分縣市</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
+          <t>客家</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>klctb.klcg.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
+          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>klctb.klcg.gov.tw</t>
+          <t>www.hakka.gov.tw</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -6207,27 +6231,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>115年海洋保育國際交流活動獎助計畫</t>
+          <t>115年品牌臺東產業行銷補助</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-319/</t>
+          <t>https://dayseechat.com/subsidy/grant-284/</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>海洋委員會</t>
+          <t>縣市政府</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>個人｜學校｜民間團體</t>
+          <t>企業｜民間團體</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>不分縣市</t>
+          <t>台東</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6237,13 +6261,13 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>生態環境</t>
+          <t>產業發展</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
@@ -6252,22 +6276,22 @@
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>www.oca.gov.tw</t>
+          <t>bdsone.taitung.gov.tw</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
+          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>www.oca.gov.tw</t>
+          <t>bdsone.taitung.gov.tw</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -6284,22 +6308,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>全國性運動團體辦理全民運動相關活動計畫</t>
+          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-300/</t>
+          <t>https://dayseechat.com/subsidy/grant-246/</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>縣市政府</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>民間團體</t>
+          <t>個人</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6309,285 +6333,50 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>100萬以上</t>
+          <t>不分金額</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>生態環境</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+          <t>婦女</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>孩童</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>身心障礙</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
+          <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>isports.sa.gov.tw</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>isports.sa.gov.tw</t>
-        </is>
-      </c>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>direct_official</t>
+          <t>search_no_match</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>客家影像畢業製作孵育計畫徵選</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-294/</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>客家委員會</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>學校</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>11萬-50萬｜51萬-100萬</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>客家</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>www.hakka.gov.tw</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>115年品牌臺東產業行銷補助</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-284/</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>企業｜民間團體</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>台東</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>10萬以下｜11萬-50萬</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>bdsone.taitung.gov.tw</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>bdsone.taitung.gov.tw</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-246/</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>衛生福利部</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>個人</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>婦女</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>孩童</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>身心障礙</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
         <is>
           <t>low</t>
         </is>
@@ -6604,7 +6393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD84"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14358,17 +14147,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-407/</t>
+          <t>https://dayseechat.com/subsidy/grant-406/</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>經濟部</t>
+          <t>文化部</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -14388,22 +14177,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>"協助因應貿易自由化加強輔導型產業參加國際展覽補助" 公告 site:www.moea.gov.tw</t>
+          <t>"115至117年傳統藝術接班人外台劇藝提升計畫" 公告 site:www.moc.gov.tw</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>www.moea.gov.tw</t>
+          <t>www.moc.gov.tw</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -14425,13 +14214,13 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>產業發展</t>
+          <t>文化藝文</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
@@ -14446,188 +14235,6 @@
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr">
-        <is>
-          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助 - 小社區大事件
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助
-計畫來源 :
-經濟部
-補助對象 :
-民間團體
-適用地區 :
-不分縣市
-補助金額 :
-不分金額
-申請文件：點我前往主辦單位網站
-截止日期 :
-2026-04-27
-產業發展
-#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
-▎ 計畫簡介
-經濟部國際貿易署為協助我國受貿易自由化衝擊之加強輔導型產業拓銷國際市場，特辦理本補助計畫。計畫針對成衣、內衣、毛巾、鞋類、家電、陶瓷等22項特定產業所屬之公協會，提供參加國際實體展覽或辦理非展覽拓銷活動的經費補助。藉由資源挹注，降低相關產業公協會帶領業者出國參展的負擔，進而提升臺灣產製產品的國際能見度與出口競爭力。
-適用對象限定：須為經濟部產業發展署認定之22項因應貿易自由化加強輔導型產業所屬公協會。
-實體展覽補助：受理開展日為115年5月1日至12月31日期間之國際實體展覽。
-臺灣產製要求：參展產品必須符合臺灣產製規範，方可列入攤位數計算及經費核銷。
-專屬攤位規範：受補助之實體展攤位僅限我國參展廠商使用，且招牌不得出現非受補助廠商名稱。
-先到先審機制：採隨到隨審方式辦理，至年度核配經費用罄為止。
-確認產業資格：申請前務必至經濟部相關網站查詢並確認所屬公協會及會員產品符合22項產業範圍。
-儘早提出申請：因採先到先審制且經費有限，建議盡速備妥文件並以掛號郵寄或專人送達。
-精準規劃展覽：選擇對所屬產業最具拓銷效益的國際目標市場展覽，並在計畫中說明參展理由與預期訂單效益。
-嚴格把關展品：確保所有參展廠商明確知悉展品須為臺灣產製的規定，避免後續核銷發生爭議。
-遵守攤位規範：規劃攤位設計時，嚴格遵守招牌及使用對象的限制，確保符合補助查核標準。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>115至117年傳統藝術接班人外台劇藝提升計畫</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-406/</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>文化部</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>民間團體</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>不分金額</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>"115至117年傳統藝術接班人外台劇藝提升計畫" 公告 site:www.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>www.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=115至117年傳統藝術接班人外台劇藝提升計畫</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>www.google.com</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr">
         <is>
           <t>115至117年傳統藝術接班人外台劇藝提升計畫 - 小社區大事件
 首頁
@@ -14719,113 +14326,113 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-402/</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>個人｜學校｜民間團體</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>台南</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>"臺南青年公共參與行動計畫" 公告 site:www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺南青年公共參與行動計畫</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>創新創業</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>青年</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr">
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>115年臺南青年公共參與行動計畫 - 小社區大事件
 首頁
@@ -14936,97 +14543,97 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-394/</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>文化部</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>個人｜民間團體</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>51萬-100萬</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>"文化部青年村落文化行動計畫" 公告 site:www.moc.gov.tw</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>www.moc.gov.tw</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年文化部青年村落文化行動計畫</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr">
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr">
         <is>
           <t>115年文化部青年村落文化行動計畫 - 小社區大事件
 首頁
@@ -15123,101 +14730,101 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-395/</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>經濟部</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>100萬以上</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>"經濟部中小企業創新研發AI轉型補助計畫" 公告 site:www.moea.gov.tw</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>www.moea.gov.tw</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度經濟部中小企業創新研發AI轉型補助計畫</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>創新創業</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr">
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
         <is>
           <t>115年度經濟部中小企業創新研發AI轉型補助計畫 - 小社區大事件
 首頁
@@ -15314,97 +14921,97 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-399/</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>個人</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>新竹</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>"新竹市政府青年AI數位工具補助" 公告 site:www.hccg.gov.tw</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>www.hccg.gov.tw</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=2026新竹市政府青年AI數位工具補助</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>青年</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr">
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr">
         <is>
           <t>2026新竹市政府青年AI數位工具補助 - 小社區大事件
 首頁
@@ -15500,93 +15107,93 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-401/</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>衛生福利部</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>個人</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>100萬以上｜10萬以下｜11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度不孕症試管嬰兒補助3.0方案</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>孩童</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr">
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr">
         <is>
           <t>115年度不孕症試管嬰兒補助3.0方案 - 小社區大事件
 首頁
@@ -15685,97 +15292,97 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-390/</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>其他對象｜民間團體</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>台中</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>"台中市公寓大廈成立管理委員會補助" 公告 site:www.taichung.gov.tw</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>www.taichung.gov.tw</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度台中市公寓大廈成立管理委員會補助</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr">
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr">
         <is>
           <t>115年度台中市公寓大廈成立管理委員會補助 - 小社區大事件
 首頁
@@ -15872,101 +15479,101 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-391/</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>台南</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>"臺南地方產業原鄉永續小旅行振興計畫" 公告 site:www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr">
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr">
         <is>
           <t>115年臺南地方產業原鄉永續小旅行振興計畫 - 小社區大事件
 首頁
@@ -16063,97 +15670,97 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-392/</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>台南</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>"臺南市民旅遊補助計畫" 公告 site:www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年臺南市民旅遊補助計畫</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr">
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr">
         <is>
           <t>115年臺南市民旅遊補助計畫 - 小社區大事件
 首頁
@@ -16249,97 +15856,97 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-393/</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>不分金額</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>"第2期臺北市觀光活動補助" 公告 site:www.gov.taipei</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>www.gov.taipei</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年度第2期臺北市觀光活動補助</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr">
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr">
         <is>
           <t>115年度第2期臺北市觀光活動補助 - 小社區大事件
 首頁
@@ -16435,101 +16042,101 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>115年親海無礙海洋創生行動方案</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-375/</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>海洋委員會</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>學校｜民間團體</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>不分金額</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年親海無礙海洋創生行動方案</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>"親海無礙海洋創生行動方案" 公告 site:www.oac.gov.tw</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>www.oac.gov.tw</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115年親海無礙海洋創生行動方案</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr">
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr">
         <is>
           <t>115年親海無礙海洋創生行動方案 - 小社區大事件
 首頁
@@ -16636,97 +16243,97 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>2026-2027高雄馬祖團體旅遊補助計畫</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-383/</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>連江｜高雄</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>"2027高雄馬祖團體旅遊補助計畫" 公告 site:www.kcg.gov.tw</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>www.kcg.gov.tw</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=2026高雄馬祖團體旅遊補助計畫</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr">
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr">
         <is>
           <t>2026-2027高雄馬祖團體旅遊補助計畫 - 小社區大事件
 首頁
@@ -16822,89 +16429,89 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-385/</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>台南</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.twtainan.net/</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
         <is>
           <t>https://www.twtainan.net/</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>www.twtainan.net</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr">
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr">
         <is>
           <t>115年臺南市民旅遊補助計畫臺南地方產業原鄉永續小旅行振興計畫 - 小社區大事件
 首頁
@@ -16999,97 +16606,97 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>115年度高雄市公寓大廈共用部分維護修繕費用補助</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-381/</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>其他對象</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>高雄</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>不分金額</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>"高雄市公寓大廈共用部分維護修繕費用補助" 公告 site:www.kcg.gov.tw</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>www.kcg.gov.tw</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115%E5%B9%B4%E5%BA%A6%E9%AB%98%E9%9B%84%E5%B8%82%E5%85%AC%E5%AF%93%E5%A4%A7%E5%BB%88%E5%85%B1%E7%94%A8%E9%83%A8%E5%88%86%E7%B6%AD%E8%AD%B7%E4%BF%AE%E7%B9%95%E8%B2%BB%E7%94%A8%E8%A3%9C%E5%8A%A9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>2026-12-01</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr">
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr">
         <is>
           <t>115年度高雄市公寓大廈共用部分維護修繕費用補助 - 小社區大事件
 首頁
@@ -17184,97 +16791,97 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>115年臺南市家戶屋頂設置太陽光電加速計畫</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-380/</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>個人</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>台南</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>100萬以上｜10萬以下</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>"臺南市家戶屋頂設置太陽光電加速計畫" 公告 site:www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>www.tainan.gov.tw</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=115%E5%B9%B4%E8%87%BA%E5%8D%97%E5%B8%82%E5%AE%B6%E6%88%B6%E5%B1%8B%E9%A0%82%E8%A8%AD%E7%BD%AE%E5%A4%AA%E9%99%BD%E5%85%89%E9%9B%BB%E5%8A%A0%E9%80%9F%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr">
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr">
         <is>
           <t>115年臺南市家戶屋頂設置太陽光電加速計畫 - 小社區大事件
 首頁
@@ -17370,101 +16977,101 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>115年度新北市低碳社區改造補助</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-378/</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>其他對象</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>新北</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>10萬以下｜11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
         <is>
           <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>www.epd.ntpc.gov.tw</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>https://www.epd.ntpc.gov.tw/StaticPage/low-carbon-community-renovation-subsidies</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>www.epd.ntpc.gov.tw</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr">
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr">
         <is>
           <t>115年度新北市低碳社區改造補助 - 小社區大事件
 首頁
@@ -17562,97 +17169,97 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>115年文化部社造築夢培養皿徵選獎勵計畫</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-387/</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>文化部</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>個人</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
         <is>
           <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>www.moc.gov.tw</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>https://www.moc.gov.tw/News_Content.aspx?n=105&amp;s=251954</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>www.moc.gov.tw</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr">
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr">
         <is>
           <t>115年文化部社造築夢培養皿徵選獎勵計畫 - 小社區大事件
 首頁
@@ -17748,97 +17355,97 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>115年度台中市都市更新整建維護補助計畫</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-369/</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>台中</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>51萬-100萬</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
         <is>
           <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>www.taichung.gov.tw</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>https://www.taichung.gov.tw/3234351/post</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>www.taichung.gov.tw</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr">
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr">
         <is>
           <t>115年度台中市都市更新整建維護補助計畫 - 小社區大事件
 首頁
@@ -17933,97 +17540,97 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>115年度台中市公寓大廈成立管委會獎勵補助計畫</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-370/</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>台中</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>11萬-50萬</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
         <is>
           <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>thd.taichung.gov.tw</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>https://thd.taichung.gov.tw/981499/981508/981517/981521/3361862</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>thd.taichung.gov.tw</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr">
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr">
         <is>
           <t>115年度台中市公寓大廈成立管委會獎勵補助計畫 - 小社區大事件
 首頁
@@ -18118,101 +17725,101 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>115年度臺北市住宅社區創能儲能及節能補助計畫</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-371/</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>個人｜民間團體</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
         <is>
           <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>www.gov.taipei</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>https://www.gov.taipei/News_Content.aspx?n=D0042A87C2F0270A&amp;sms=78D644F2755ACCAA&amp;s=8719C5A1FBD1AC51</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>www.gov.taipei</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr">
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr">
         <is>
           <t>115年度臺北市住宅社區創能儲能及節能補助計畫 - 小社區大事件
 首頁
@@ -18310,89 +17917,89 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>115年度臺北市產業發展獎勵補助計畫SITI</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-363/</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>台北</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>100萬以上</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>https://www.industry-incentive.taipei/</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
         <is>
           <t>https://www.industry-incentive.taipei/</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>www.industry-incentive.taipei</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr">
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr">
         <is>
           <t>115年度臺北市產業發展獎勵補助計畫SITI - 小社區大事件
 首頁
@@ -18487,89 +18094,89 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>115年度小型企業創新研發計畫SBIR</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-365/</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>經濟部</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>100萬以上</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://sbir.org.tw/</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
         <is>
           <t>https://sbir.org.tw/</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>sbir.org.tw</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr">
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr">
         <is>
           <t>115年度小型企業創新研發計畫SBIR - 小社區大事件
 首頁
@@ -18664,97 +18271,97 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>115年度推動工作與生活平衡補助計畫</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-368/</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>勞動部</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>企業｜學校｜民間團體</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
         <is>
           <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>wlb.mol.gov.tw</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>https://wlb.mol.gov.tw/Page/Grants/GrantApplication.aspx</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>wlb.mol.gov.tw</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>高齡</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr">
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr">
         <is>
           <t>115年度推動工作與生活平衡補助計畫 - 小社區大事件
 首頁
@@ -18852,97 +18459,97 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>115年度彰化縣地方型SBIR產業創新研發計畫</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-361/</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>彰化</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>51萬-100萬</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
         <is>
           <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>www.chcg.gov.tw</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>https://www.chcg.gov.tw/ch2/newsdetail.aspx?bull_id=427027&amp;utm_source=website&amp;utm_medium=rss&amp;utm_campaign=news01b</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>www.chcg.gov.tw</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr">
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr">
         <is>
           <t>115年度彰化縣地方型SBIR產業創新研發計畫 - 小社區大事件
 首頁
@@ -19037,89 +18644,89 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>商業服務業AI解決方案補助計畫</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-359/</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>經濟部</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>51萬-100萬</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
         <is>
           <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>www.smebiz.org.tw</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr">
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr">
         <is>
           <t>商業服務業AI解決方案補助計畫 - 小社區大事件
 首頁
@@ -19214,97 +18821,97 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-351/</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>桃園</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>11萬-50萬</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
         <is>
           <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>tyoem.tycg.gov.tw</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>https://tyoem.tycg.gov.tw/News_Content.aspx?n=21952&amp;sms=19830&amp;s=1608773</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>tyoem.tycg.gov.tw</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
-      <c r="AB68" t="inlineStr"/>
-      <c r="AC68" t="inlineStr"/>
-      <c r="AD68" t="inlineStr">
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr">
         <is>
           <t>桃園市旅宿業減少塑膠瓶裝水行動補助計畫 - 小社區大事件
 首頁
@@ -19399,463 +19006,101 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>中小企業接班轉型計畫</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-353/</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>雙百萬運動漫畫徵選</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-344/</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>文化部</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>企業｜學校｜民間團體</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>100萬以上</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>www.value-chain.com.tw</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>direct_non_google</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>grants.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>grants.moc.gov.tw</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>文化藝文</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>中小企業接班轉型計畫 - 小社區大事件
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-中小企業接班轉型計畫
-計畫來源 :
-經濟部
-補助對象 :
-企業
-適用地區 :
-不分縣市
-補助金額 :
-100萬以上
-申請文件：點我前往主辦單位網站
-截止日期 :
-2026-04-27
-產業發展
-#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
-▎ 計畫簡介
-計畫背景
-本計畫旨在協助中小企業在接班階段進行有效的數位轉型，透過補助支持企業接班人主導的商業模式轉型與數位科技應用。計畫強調企業需在一年內完成轉型成果，並以可驗證的方式展現新市場、新通路及數位化能力，幫助企業在競爭中立於不敗之地。
-條列補助5大重點
-1. 補助上限：最高800萬元
-2. 補助比例：政府補助款不得超過總經費50%
-3. 申請截止時間：115年4月27日17:30
-4. 申請資格：合併年營收20億以下的企業
-5. 計畫期程：不超過1年
-條列計畫撰寫5大技巧
-1. 確保計畫主持人為接班人，並能清楚表達轉型藍圖及驗證設計。
-2. 提供具體的商業模式轉型方案，明確說明新市場或新通路的定位及策略。
-3. 整理數位科技應用的具體方式，包括如何提升供應鏈與客戶關係管理。
-4. 準備小範圍概念驗證的證據，顯示已有的PoC成果。
-5. 提前準備自籌款項，確保計畫能在一年內落地執行，並考量人力資源及跨部門協作。</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-356/</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>經濟部</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>企業</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>keid.nat.gov.tw</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>keid.nat.gov.tw</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
-      <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助 - 小社區大事件
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-首頁
-關於我們
-我們是誰
-發展歷程
-加入我們
-找資訊
-找知識
-好文學-社區工作技巧
-地方學- 社區案例分享
-找資源
-數位導覽AI.Trip
-文創美編設計
-聯絡我們
-帳號設定
-註冊
-中小製造業接班傳承AI應用數位轉型主題式研發計畫補助
-計畫來源 :
-經濟部
-補助對象 :
-企業
-適用地區 :
-不分縣市
-補助金額 :
-100萬以上
-申請文件：點我前往主辦單位網站
-截止日期 :
-2026-04-27
-產業發展
-#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
-▎ 計畫簡介
-計畫背景
-為協助中小型製造業者運用數位科技達成數位轉型目標，創造新商業模式，提供補助資源，鼓勵企業接班人透過創新思考模式，主導或協助公司進行數位轉型，重塑企業DNA建立新思維，並促使企業完成接班。經濟部產業發展署特推動本計畫，以支持業者的轉型與創新。
-補助重點
-1. 每案政府補助經費以新臺幣800萬元為上限。
-2. 政府補助經費占總計畫經費50%為上限。
-3. 申請期限至115年4月27日止。
-4. 申請業者須符合中小型製造業者的資格。
-5. 計畫執行時間以1年為上限。
-計畫撰寫技巧
-1. 明確定義計畫目標，確保計畫內容符合數位轉型的需求，強調如何透過AI技術改變商業模式。
-2. 梳理出清晰的執行步驟，將計畫分為不同階段，讓審查者易於理解。
-3. 提供具體的財務預算，並明確指出補助金額的使用計畫，增加透明度。
-4. 強調團隊的專業能力及過往成功案例，增強信任感。
-5. 定期檢視和調整計畫進度，確保每個階段的目標都能夠如期完成，並隨時與相關單位溝通進度。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>雙百萬運動漫畫徵選</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-344/</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>文化部</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>企業｜學校｜民間團體</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>不分縣市</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>100萬以上</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>https://grants.moc.gov.tw/Web/PointDetail.jsp?__viewstate=oRWyc5VpG+OgRsrb7EaY6d9VoePEva5e7oJCOHz4L408lIe/efs7z+WTtc3mBJBkYvZhpy/Mg9Q=</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>grants.moc.gov.tw</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>direct_official</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>文化藝文</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr">
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr">
         <is>
           <t>雙百萬運動漫畫徵選 - 小社區大事件
 首頁
@@ -19953,101 +19198,101 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>115年桃園市智慧科技農業專案補助計畫</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-345/</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>個人｜民間團體</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>桃園</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
         <is>
           <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>www.guishan.tycg.gov.tw</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>https://www.guishan.tycg.gov.tw/News_Content.aspx?n=7695&amp;s=1608415</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>www.guishan.tycg.gov.tw</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>農漁村議題</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr"/>
-      <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr">
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr">
         <is>
           <t>115年桃園市智慧科技農業專案補助計畫 - 小社區大事件
 首頁
@@ -20145,89 +19390,89 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>商業服務業AI解決方案補助計畫</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-349/</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>經濟部</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>企業</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
         <is>
           <t>https://www.smebiz.org.tw/project-tenacity_shop.php</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>www.smebiz.org.tw</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>2027-10-20</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
-      <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr">
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr">
         <is>
           <t>商業服務業AI解決方案補助計畫 - 小社區大事件
 首頁
@@ -20322,89 +19567,89 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>基隆市青年參與公益活動補助計畫</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-389/</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>學校｜民間團體</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>基隆</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>11萬-50萬</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
         <is>
           <t>https://dsa.dyhu.edu.tw/p/404-1021-62035.php?Lang=zh-tw</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>dsa.dyhu.edu.tw</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
         <is>
           <t>青年</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
-      <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr">
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr">
         <is>
           <t>基隆市青年參與公益活動補助計畫 - 小社區大事件
 首頁
@@ -20500,101 +19745,101 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>115年度推動事業單位辦理職前培訓計畫</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-334/</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>勞動部</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>企業｜學校</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>台中</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>51萬-100萬</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
         <is>
           <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>tcnr.wda.gov.tw</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>https://tcnr.wda.gov.tw/News_Content.aspx?n=9CDFC65181CC2AEA&amp;sms=68798FA6FAE753EC&amp;s=7096E023258FDA09</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>tcnr.wda.gov.tw</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>2026-10-31</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>青年</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr">
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr">
         <is>
           <t>115年度推動事業單位辦理職前培訓計畫 - 小社區大事件
 首頁
@@ -20691,89 +19936,89 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>親愛文化攜手計畫</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-336/</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>學校｜民間團體</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>南投</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>11萬-50萬</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>https://cacf.easy.co/pages/support</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
         <is>
           <t>https://cacf.easy.co/pages/support</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>cacf.easy.co</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
         <is>
           <t>direct_non_google</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
         <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr">
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr">
         <is>
           <t>親愛文化攜手計畫 - 小社區大事件
 首頁
@@ -20869,101 +20114,101 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-331/</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>基隆</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>100萬以上｜10萬以下</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
         <is>
           <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>www.klcg.gov.tw</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>https://www.klcg.gov.tw/tw/social/2636-311439.html</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>www.klcg.gov.tw</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
         <is>
           <t>社區議題</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>高齡</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="inlineStr"/>
-      <c r="AD77" t="inlineStr">
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr">
         <is>
           <t>基隆市115年布建社區照顧關懷據點及巷弄長照站實施計畫 - 小社區大事件
 首頁
@@ -21060,181 +20305,275 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>115年度高雄市觀光行銷推廣補助計畫</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-327/</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>高雄</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>10萬以下｜11萬-50萬</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>khh.travel</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>115年度高雄市觀光行銷推廣補助計畫 - 小社區大事件
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+首頁
+關於我們
+我們是誰
+發展歷程
+加入我們
+找資訊
+找知識
+好文學-社區工作技巧
+地方學- 社區案例分享
+找資源
+數位導覽AI.Trip
+文創美編設計
+聯絡我們
+帳號設定
+註冊
+115年度高雄市觀光行銷推廣補助計畫
+計畫來源 :
+縣市政府
+補助對象 :
+民間團體
+適用地區 :
+高雄
+補助金額 :
+10萬以下
+11萬-50萬
+申請文件：點我前往主辦單位網站
+截止日期 :
+2026-11-30
+產業發展
+#本資訊為AI生成工具協助彙整，若有誤差請以原主辦單位網站資料為主．
+▎ 計畫簡介
+計畫背景
+高雄市政府為了促進觀光產業的發展，特別推出115年度觀光行銷推廣補助計畫，旨在透過各種行銷活動吸引更多旅客來訪，進而提升本市的觀光收益。計畫的執行對於提升高雄的知名度及吸引力具有重要意義，尤其是在全球旅遊逐漸復甦的背景下，這項補助計畫將為業者提供必要的支持，鼓勵他們積極參與行銷推廣活動，並提升服務品質，讓更多遊客感受到高雄的魅力。
+條列補助5大重點
+1. 補助對象包括法人、團體及業者。
+2. 每年對同一團體的補助金額上限為2萬5,000元。
+3. 補助項目包括參與國外旅展及推廣活動。
+4. 申請補助金額10萬元以上需提前30天申請。
+5. 申請補助10萬元（含）以下需提前3天申請。
+條列計畫撰寫5大技巧
+1. 明確定義計畫目標：在撰寫計畫時，應清楚說明計畫的目的，例如希望透過行銷活動提升旅客數量。
+2. 詳細描述計畫內容：具體列出將參與的活動，如國外旅展的名稱、時間及地點等，讓審核者能夠清楚了解計畫的可行性。
+3. 提供預算明細：清楚列出預算分配，包括各項活動的預算及預期效益，讓補助機關了解資金的使用計畫。
+4. 強調團隊能力：介紹負責計畫的團隊成員及其相關經驗，增加計畫的可信度。
+5. 準時提交申請：根據計畫的要求，確保在截止日期前提交完整的申請文件，以免影響補助的獲得。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>115年度補助文化活動作業</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-314/</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>縣市政府</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>個人｜民間團體</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>基隆</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>10萬以下</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>"高雄市觀光行銷推廣補助計畫" 公告 site:www.kcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>www.kcg.gov.tw</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-327/</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>dayseechat.com</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>search_no_match</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>2026-11-30</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>產業發展</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>115年度補助文化活動作業</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>https://dayseechat.com/subsidy/grant-314/</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>縣市政府</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>個人｜民間團體</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>基隆</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>10萬以下</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
         <is>
           <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>klctb.klcg.gov.tw</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>https://klctb.klcg.gov.tw/News_Content.aspx?n=7458&amp;s=16555</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>klctb.klcg.gov.tw</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr">
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
         <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
-      <c r="AC79" t="inlineStr"/>
-      <c r="AD79" t="inlineStr">
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr">
         <is>
           <t>115年度補助文化活動作業 - 小社區大事件
 首頁
@@ -21330,97 +20669,97 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>115年海洋保育國際交流活動獎助計畫</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-319/</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>海洋委員會</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>個人｜學校｜民間團體</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
         <is>
           <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>www.oca.gov.tw</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>https://www.oca.gov.tw/ch/home.jsp?id=244&amp;parentpath=0,2&amp;mcustomize=bulletin_view.jsp&amp;dataserno=202512120006&amp;mserno=201910190001</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>www.oca.gov.tw</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr">
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr">
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr">
         <is>
           <t>115年海洋保育國際交流活動獎助計畫 - 小社區大事件
 首頁
@@ -21518,97 +20857,97 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>全國性運動團體辦理全民運動相關活動計畫</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-300/</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>100萬以上</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
         <is>
           <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>isports.sa.gov.tw</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>https://isports.sa.gov.tw/apps/News.aspx?SYS=TIS&amp;PKNO=7024</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>isports.sa.gov.tw</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>2026-12-15</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr">
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
         <is>
           <t>生態環境</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="inlineStr"/>
-      <c r="AD81" t="inlineStr">
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr">
         <is>
           <t>全國性運動團體辦理全民運動相關活動計畫 - 小社區大事件
 首頁
@@ -21703,101 +21042,101 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>客家影像畢業製作孵育計畫徵選</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-294/</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>客家委員會</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>學校</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>11萬-50萬｜51萬-100萬</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
         <is>
           <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>www.hakka.gov.tw</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>https://www.hakka.gov.tw/chhakka/app/data/view?module=hotnews&amp;id=25&amp;serno=dc594ee6-16cd-4720-807a-1cdbbdc3adfd</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>www.hakka.gov.tw</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr">
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
         <is>
           <t>客家</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>文化藝文</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr">
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr">
         <is>
           <t>客家影像畢業製作孵育計畫徵選 - 小社區大事件
 首頁
@@ -21894,97 +21233,97 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>115年品牌臺東產業行銷補助</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-284/</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>縣市政府</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>企業｜民間團體</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>台東</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
         <is>
           <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>bdsone.taitung.gov.tw</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>https://bdsone.taitung.gov.tw/article.html?id=300</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>bdsone.taitung.gov.tw</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>direct_official</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
         <is>
           <t>產業發展</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="inlineStr"/>
-      <c r="AD83" t="inlineStr">
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr">
         <is>
           <t>115年品牌臺東產業行銷補助 - 小社區大事件
 首頁
@@ -22081,101 +21420,101 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>https://dayseechat.com/subsidy/grant-246/</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>衛生福利部</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>個人</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>不分縣市</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>不分金額</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>衛生福利部社會及家庭署114年單親扶助計畫</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
         <is>
           <t>https://www.google.com/search?q=%E8%A1%9B%E7%94%9F%E7%A6%8F%E5%88%A9%E9%83%A8%E7%A4%BE%E6%9C%83%E5%8F%8A%E5%AE%B6%E5%BA%AD%E7%BD%B2114%E5%B9%B4%E5%96%AE%E8%A6%AA%E6%89%B6%E5%8A%A9%E8%A8%88%E7%95%AB</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>www.google.com</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
         <is>
           <t>search_no_match</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
         <is>
           <t>婦女</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>孩童</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>身心障礙</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
-      <c r="AB84" t="inlineStr"/>
-      <c r="AC84" t="inlineStr"/>
-      <c r="AD84" t="inlineStr">
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr">
         <is>
           <t>衛生福利部社會及家庭署114年單親扶助計畫 - 小社區大事件
 首頁
@@ -22315,7 +21654,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B2" t="n">
         <v>83</v>
@@ -22327,7 +21666,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -22573,10 +21912,14 @@
           <t>民間團體</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>高雄</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10萬以下</t>
+          <t>10萬以下｜11萬-50萬</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -22596,24 +21939,24 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>https://dayseechat.com/subsidy/grant-327/</t>
+          <t>https://khh.travel/zh-tw/event/news/7268/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>dayseechat.com</t>
+          <t>khh.travel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>search_no_match</t>
+          <t>direct_non_google</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -22628,7 +21971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22725,6 +22068,221 @@
       <c r="S1" t="inlineStr">
         <is>
           <t>official_url_confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-407/</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>民間團體</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>不分金額</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=115年度協助因應貿易自由化加強輔導型產業參加國際展覽補助</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>www.google.com</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>search_no_match</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>中小企業接班轉型計畫</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-353/</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://www.value-chain.com.tw/news_info.asp?id=731</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>www.value-chain.com.tw</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>direct_non_google</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>中小製造業接班傳承AI應用數位轉型主題式研發計畫補助</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://dayseechat.com/subsidy/grant-356/</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>經濟部</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>企業</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>不分縣市</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>100萬以上</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>產業發展</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>keid.nat.gov.tw</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://keid.nat.gov.tw/cloud/Web/project_description.aspx</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>keid.nat.gov.tw</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>direct_official</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
